--- a/校园招聘/制造业/制造业通用/技术研发类/自动化工程师/4_需重新出答案/3轮_制造业通用_自动化工程师_重新出答案.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/自动化工程师/4_需重新出答案/3轮_制造业通用_自动化工程师_重新出答案.xlsx
@@ -413,86 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>技能分类</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>第一层</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>第二层</t>
+          <t>知识点</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>第三层</t>
+          <t>难度</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>技能分类</t>
+          <t>行业</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>岗位</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>知识点</t>
+          <t>招聘场景</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>难度</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>行业</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>岗位</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>招聘场景</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>提示词</t>
         </is>
@@ -501,3764 +466,2576 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>在一条多工位连续输送的装配产线上，PLC需同时采集12个接近开关信号和8个气缸到位反馈信号，但当前I/O模块物理点数已满，且部分输入通道存在共地限制、抗干扰能力差异及响应时间要求不一的情况。请简述你如何统筹规划这20个信号的I/O点位映射策略，并说明关键决策依据。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I/O点位映射是指根据信号类型、电气特性与工艺需求，将现场传感器信号合理分配到PLC可用输入通道的过程，核心是兼顾信号可靠性、响应及时性与硬件资源约束。</t>
+          <t>PLC程序设计</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>常见方案有四种：一是复用高速计数通道接入关键接近开关，但仅适用于脉冲类信号，不适用本题的开关量；二是加装扩展I/O模块，实施简单但受机柜空间与背板带宽限制；三是采用智能IO设备就近采集后汇总通信，适合长距离布线场景但增加调试复杂度；四是按信号优先级重分配现有通道——把对响应快、抗干扰强要求高的气缸到位信号优先安排在独立隔离、响应快的通道上，把相对缓变的接近开关信号整合到共地组内。综合评估，第四种最贴合产线实际，既不改动硬件结构，又能通过逻辑分组实现资源优化。</t>
+          <t>I/O点位映射</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1个异常情况概要：某气缸到位信号频繁误触发。具体情况：该信号与变频器动力线同槽敷设，未做屏蔽分离，导致感应干扰使PLC误读为‘到位’。解决思路：现场核查布线路径，将该信号线单独穿金属管并单端接地，同时在PLC端启用软件滤波功能。1个复杂问题概要：共地组内多个接近开关信号出现串扰。具体问题：同一COM端下3个接近开关中1个动作时，另2个电平被拉低。解决思路：测量各传感器漏电流与COM端驱动能力，更换为低功耗型传感器或拆分共地组，将高漏电设备单独配COM端。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PLC程序设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I/O点位映射</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>在一条多工位装配线上，某伺服轴需同时满足：频繁启停的定位精度要求（±0.02mm），以及连续往复运动时的动态刚性需求（抵抗机械振动导致的位置漂移）。若仅使用单一伺服控制模式难以兼顾，请简述应如何分阶段配置位置模式与转矩模式，并说明切换边界判定所依赖的实时运动参数及其工程依据。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>位置模式适合启停阶段，靠脉冲或总线指令闭环控制位置，保证±0.02mm定位精度；转矩模式适合高速往复段，直接控制输出力矩，抑制振动引起的微小位移。两种模式需按运动状态分阶段使用，不能混用或固定配置。</t>
+          <t>伺服控制</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是基于速度阈值切换，当轴速超过设定值（如30%额定速度）切入转矩模式，响应快但易受加减速干扰；二是结合速度与加速度双参数判定，更稳定，但PLC运算负担略增；三是引入位置误差动态阈值，误差持续超限则切回位置模式纠偏。综合来看，第二种最常用——既避开低速抖动误判，又避免高频切换，符合产线节拍稳定、维护简便的工程实际。</t>
+          <t>伺服控制模式区别</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1个异常情况概要：模式切换瞬间出现位置跳变。具体情况是PLC发切换指令后，伺服驱动器内部控制环未完成参数重载，导致短暂失控或指令中断。解决思路是启用驱动器的平滑切换功能，在切换前同步位置反馈和转矩指令初值，并在PLC侧插入5～10毫秒等待窗口。1个复杂问题概要：往复段末端因惯性产生微振，导致转矩模式下位置缓慢漂移。具体问题是振动频率接近机械谐振点，单纯调高刚性会引发啸叫。解决思路是结合PLC周期性采集编码器瞬时位置波动幅值，在漂移超±0.01mm且波动频率集中于某频段时，触发短时位置模式介入补偿，再平滑切回转矩模式。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>伺服控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>伺服控制模式区别</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>一条食品包装产线升级时，在保留原有主回路（含大功率加热单元和液压泵电机）的前提下新增视觉检测模块，其PLC数字量输入端口频繁出现偶发性信号跳变。现场确认控制电源与主回路共用同一配电柜母排，且图纸中未体现主回路滤波与控制回路隔离的协同设计。请结合主回路与控制回路在能量层级、干扰路径及接地策略上的本质差异，说明图纸层面应如何重构这两类回路的接口关系。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主回路负责高能量电能传输，承载大电流、高电压、强瞬态冲击；控制回路只处理低能量信号，对电压波动和电磁干扰极其敏感。两者在图纸上必须物理分隔、供电独立、接地分离，不能共用母排、共用零线、共用地线节点。</t>
+          <t>电气图纸设计</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>图纸重构有四种常用方式：一是为控制回路单独配置隔离变压器供电，抗共模干扰强但成本略高；二是主回路侧加装进线滤波器并明确标注滤波器输出端专供控制电源，实施便捷但需校核滤波器散热空间；三是控制回路采用双绕组直流电源模块，从主回路取电但实现电气隔离，性价比高但需验证纹波抑制能力；四是将PLC及视觉模块的电源、I/O端子、接地全部划入独立控制分区，并在图纸中用不同颜色和图例严格区分。综合来看，第二种方式最平衡——既利用现有配电柜空间，又能在图纸上清晰定义滤波器位置、参数和下游归属，便于施工与验收。</t>
+          <t>主回路与控制回路区别</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1个异常情况概要：控制端口信号跳变反复出现在设备启停瞬间。具体情况：主回路电机启停造成母排电压暂降与高频传导干扰，通过共用母排耦合至控制电源。解决思路：在图纸中强制要求滤波器安装在主回路断路器下口、控制电源上级，并标注‘滤波器输出端不得接入任何主回路负载’。1个复杂问题概要：改造后仍存在间歇性误触发。具体问题：主回路与控制回路虽分设地线，但最终汇入同一接地极，形成接地环流。解决思路：图纸中须明确‘控制接地系统采用单点接地方式，独立引至配电柜内专用接地铜排，该铜排仅连接控制类设备，不与主回路接地排电气连通’。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>电气图纸设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>主回路与控制回路区别</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>在液压压机控制系统中，上升和下降电磁阀线圈回路间设置了电气互锁。当操作人员连续按下上升和下降按钮时，这种互锁能保证设备处于什么安全状态？请简述其原理实现的关键点。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>能保证设备处于静止不动的安全状态，即两个动作指令同时发出时，系统不执行任何运动输出。原理关键点是：在上升和下降的控制回路中，分别串入对方接触器的常闭辅助触点，形成相互制约；任一回路得电时，自动切断另一回路的供电通路。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>实际工程中主要有三种实现方式：一是纯继电器硬接线互锁，响应快、可靠性高，但布线复杂、修改困难；二是PLC程序软互锁，灵活性好、便于调试，但依赖扫描周期，存在微秒级响应延迟风险；三是硬软双重互锁，兼顾安全与可维护性，是当前主流做法。综合来看，双重互锁最优——既满足功能安全基本要求，又便于后期逻辑调整和故障溯源，符合自动化工程师日常维护与优化的实际工作节奏。</t>
+          <t>电气互锁原理</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1个异常情况概要：互锁失效导致两个电磁阀同时得电。具体情况：接触器辅助触点粘连或PLC输出模块异常输出，使上升下降线圈同时通电，引发液压系统压力冲突甚至管路爆裂。解决思路：定期检查接触器触点状态，结合运行日志比对PLC输出与实际线圈电压，建立互锁状态实时反馈验证机制。1个复杂问题概要：操作员误操作叠加急停恢复后动作紊乱。具体问题：急停复位瞬间若按钮仍被持续按压，可能绕过互锁初始判断条件，造成逻辑竞争。解决思路：在控制逻辑中加入‘按钮释放确认’环节，要求双按钮均松开后再允许新指令生效，并设置最小指令间隔时间窗口。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>电气互锁原理</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>在工厂自动化设备中，接近开关常用于检测金属部件的位置，如果它提供的是NPN型和PNP型两种输出方式，它们在接入PLC数字量输入模块时，接线方式的关键区别是什么？请简述。</t>
+          <t>自动化设备基础</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NPN型接近开关输出端需接到PLC输入端的公共端（通常是24V负极侧），信号线接PLC输入点；PNP型则相反，输出端接PLC输入端的公共端（通常是24V正极侧），信号线同样接PLC输入点。本质区别在于电流流向不同：NPN是电流从PLC输入点流出、经传感器回到公共端；PNP是电流从公共端流出、经传感器流入PLC输入点。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>实际工作中常用三种接线方案：一是统一选用与PLC输入模块类型匹配的传感器，比如PLC输入公共端为源型（接24V+）就配PNP，为漏型（接24V−）就配NPN，可靠性最高、调试最省时；二是通过外加继电器或信号转换模块兼容混用，但增加故障点和维护成本；三是部分新型PLC支持双模式输入，可通过跳线或软件配置切换，灵活性好但需确认模块手册支持且现场已启用该功能。综合来看，第一种方案最稳妥，既符合产线标准化要求，又避免后期因接线错误导致输入点反复烧毁或信号抖动。</t>
+          <t>传感器信号输出类型区别</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1个异常情况概要：PLC输入点无响应但传感器供电正常。具体情况：现场误将PNP传感器接到漏型输入模块，或NPN接到源型模块，造成回路无法闭合。解决思路：先确认PLC输入模块公共端接线方式，再用万用表测输入点对公共端电压变化，结合传感器动作状态判断电流路径是否成立。1个复杂问题概要：同一产线混用NPN和PNP传感器导致PLC柜内布线混乱、故障定位困难。具体问题：维修人员难以快速识别各输入点对应传感器类型，更换备件时易接错，引发批量误动作。解决思路：在电气图纸中标注每路输入的传感器类型及公共端归属，并在PLC端子排粘贴颜色标签（如蓝色标NPN、红色标PNP），同步更新DCS/SCADA点表说明，形成可执行的现场作业规范。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>自动化设备基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>传感器信号输出类型区别</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>在自动化产线中，某关键工位需同时接入温度、光电和接近开关三类传感器，但现场控制柜的模拟量输入模块已满，数字量输入点位也所剩无几。已知这三类传感器均支持NPN/PNP双模式输出及多种信号类型（如4-20mA、0-10V、NAMUR、干接点）。请简述你如何统筹选择各传感器的信号输出类型，并说明背后对测量精度、抗干扰能力、布线成本与后续维护可扩展性的综合权衡依据。</t>
+          <t>自动化设备基础</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>温度传感器优先选4-20mA电流信号，光电和接近开关统一选PNP型干接点信号；所有传感器输出模式需与PLC输入模块的电气类型严格匹配，避免混用NPN和PNP造成信号误读或模块损坏。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>第一种方案：温度用0-10V、其余用干接点——但0-10V易受线路压降和干扰影响，长距离时精度下降明显，不适用于产线常见5米以上布线；第二种：三者全用4-20mA——虽抗干扰强，但会加剧模拟量通道紧缺，且接近/光电开关无需连续量，属资源错配；第三种：温度用4-20mA、其余用PNP干接点——兼顾精度与点位节约，PNP干接点响应快、兼容性强、接线简单，是当前产线最主流做法；第四种：引入IO-Link分线盒扩展数字点——实施周期长、需额外调试，仅在改造窗口宽裕时考虑。综合来看，第三种最平衡、落地最快、适配性最强。</t>
+          <t>传感器信号输出类型区别</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1个异常情况概要：现场出现多个接近开关信号偶发丢失。具体情况：同一线槽内混敷了4-20mA温度线与PNP干接点线，且未做分隔，高频开关动作引发感应耦合干扰。解决思路：立即物理隔离模拟量与开关量线路，干接点线改用双绞屏蔽线并单端接地，复测信号稳定性。1个复杂问题概要：产线后续要新增视觉检测工位，需预留扩展能力。具体问题：当前按最小点位配置后，PLC数字输入已无冗余，无法直接接入新传感器。解决思路：在本次布线时，为关键工位预埋带屏蔽的8芯线缆并留出2路备用通道，同时在控制柜内预留1个数字量输入模块安装位，确保6个月内可免拆线扩容。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>自动化设备基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>传感器信号输出类型区别</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>某汽车零部件装配线新增一台协作机器人工作站，其安全门、急停按钮和光幕需接入同一安全回路。当光幕被遮挡时系统应立即停止机器人运动，但安全门打开时允许在确认无风险后延时停机。请简述如何通过安全继电器的多通道输入配置与时间监控功能实现这两种不同响应逻辑，并说明为何不能仅用单通道安全继电器完成该任务。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>安全继电器需配置两个独立安全输入通道：光幕接入通道1，触发即断开输出，实现零延迟停机；安全门接入通道2，启用内置时间监控功能，设定合理延时窗口（如3秒），在此期间若操作员完成风险确认并复位，则允许暂缓停机。急停按钮需跨接在两个通道的公共安全触点上，确保任意时刻都能强制切断。单通道安全继电器无法同时区分并差异化响应两类事件，因它只能执行统一的即时切断逻辑，无法为安全门赋予可监控的延时判断能力。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>常见方案有四种：一是双通道带时间监控型安全继电器，支持通道独立配置与延时判定，响应精准且符合ISO 13850要求，是当前产线主流选择；二是安全PLC加专用安全模块，灵活性高但调试周期长、成本高，适合大型改造项目；三是组合式安全继电器堆叠，扩展性差、接线复杂，已逐步淘汰；四是基于安全控制器的软件逻辑实现，依赖编程能力，现场维护门槛高。综合时效性、可靠性与产线部署效率，双通道带时间监控的安全继电器方案最优，既满足功能分离要求，又便于现场工程师快速验证与交付。</t>
+          <t>安全继电器应用</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门延时期间光幕被意外遮挡。具体情况：操作员开门后尚未完成确认，光幕即被工件或人员遮挡，系统需立即中断延时逻辑并执行紧急停机。解决思路：将光幕信号设为高优先级硬接线直通通道1，其动作不受通道2延时状态影响，确保安全响应不被延迟逻辑阻塞。1个复杂问题概要：安全回路中多个设备共用同一安全继电器时出现误动作。具体问题：光幕与安全门信号线缆并行敷设过长导致感应干扰，引发间歇性通道误触发。解决思路：现场排查时优先检查物理布线隔离与端子压接质量，采用双绞屏蔽线分层走线，关键安全输入单独穿管，并通过继电器自诊断指示灯与手动测试模式逐项验证各通道抗扰性能。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>安全继电器应用</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>一条装配线包含多个工位，每个工位设有独立安全门，且部分工位存在共享危险区域。当任一工位安全门开启时，对应区域需立即断电停机；但若相邻工位同时开门，系统不应误判为冗余故障而抑制停机。请简述如何设计安全门联锁逻辑，确保既满足单点触发的即时性，又避免因多门协同动作引发的误抑制。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑必须基于‘单点失效即停机’原则设计：任一安全门信号有效（即门打开），对应驱动回路必须在规定安全响应时间内切断动力电源；共享区域的联锁需按物理风险边界划分，不因多个门同时动作而降低停机优先级。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是采用硬接线双通道安全继电器，各门独立接入，输出串联控制本区执行器——响应快、无通信延迟，但扩展性差；二是PLC安全模块分通道采集门信号，用‘或逻辑’触发对应区域停机，再通过区域映射表处理共享区——兼顾灵活性与确定性，是当前主流；三是用安全总线统一采集所有门状态，由安全控制器做动态区域裁决——适合大型线体，但需验证通信周期是否满足安全响应时间。综合来看，第二方案最平衡，既保障单点触发的确定性，又支持共享区域的精准归属。</t>
+          <t>安全门联锁逻辑</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门触点粘连未释放。具体情况：门已关闭但常闭触点未能复位，导致系统持续报故障并锁死停机。解决思路：在逻辑中加入门状态变化沿检测+超时确认机制，结合机械复位反馈或辅助位置开关交叉验证。1个复杂问题概要：相邻工位因工艺协同需短时同步开门作业。具体问题：两人同时开相邻门，系统误判为冗余通道异常而抑制停机。解决思路：不取消停机，而是通过增设‘协同开门使能模式’——需双人独立触发使能按钮+门状态同步窗口校验，仅在此模式下允许共享区维持动力，其余时间仍严格执行单点触发停机。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>某柔性产线采用模块化设计，安全门配置随工艺切换动态变化：同一物理门在不同生产模式下可能属于‘主危险区’或‘非危险通道’。控制系统需在不修改硬件接线的前提下，通过逻辑层实现门状态的有效屏蔽与激活。请简述该动态联锁逻辑的核心实现机制及必须验证的关键安全约束。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>核心机制是将安全门的使能状态与当前运行的工艺模式绑定，在PLC逻辑中设置模式识别标志位，据此控制该门信号是否参与安全回路的表决；关键安全约束包括：门信号仅在被判定为危险区入口时才强制接入安全回路，且屏蔽过程必须满足‘断电即失效’原则，任何模式切换不得导致安全功能临时缺失。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>常见实现方式有四种：一是用工艺模式字直接查表映射各门使能状态，响应快但扩展性弱；二是基于安全PLC的条件使能指令块，支持在线配置且符合安全认证要求，但需配套授权许可；三是通过安全总线协议的动态组态功能下发门属性，依赖设备兼容性；四是用标准PLC加双通道安全继电器组合实现逻辑裁剪，成本低但验证复杂。综合来看，采用带安全认证的条件使能指令块方案最优——它兼顾时效性、可追溯性和合规性，且无需额外硬件改动。</t>
+          <t>安全门联锁逻辑</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1个异常情况概要：模式切换瞬间门状态误判。具体情况：工艺模式切换时，新旧模式标志位更新不同步，导致某扇门短暂处于‘既未屏蔽也未激活’的中间态。解决思路：在模式切换逻辑中加入双稳态锁存和确认延时，确保门使能状态严格跟随已稳定生效的模式标识。1个复杂问题概要：多模式嵌套下的门归属冲突。具体问题：某门在A模式属危险区、B模式属非危险通道，而C模式同时调用A与B子流程，引发联锁逻辑歧义。解决思路：建立模式优先级树结构，在PLC中按预设层级进行归属仲裁，并在HMI上实时可视化门当前安全角色，供操作员复核。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>一条产线中多台伺服驱动器通过EtherCAT总线与主站通信，近期出现间歇性位置偏差，且故障复现周期长。若用报文抓取分析定位问题，你将如何设计抓取策略来区分是物理层干扰、协议栈异常还是主站调度缺陷？请说明关键抓取位置、时间窗口选择依据及三类问题在报文特征上的核心差异。</t>
+          <t>故障诊断与可靠性</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>我会在主站出口侧、末端从站回环口、以及关键中间节点的物理端口同步抓取报文；时间窗口要覆盖完整运动周期，并叠加故障前后的动态窗口；物理层干扰表现为帧校验失败和重复重发，协议栈异常体现为过程数据错序或状态机跳变，主站调度缺陷则反映为周期抖动超限和命令下发延迟不一致。</t>
+          <t>通信故障诊断</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>常用方案有三种：一是单点主站抓包，优点是部署快但无法区分上下游问题；二是全链路分段抓包，能准确定位故障段但需协调多台设备接入；三是触发式循环缓存抓包，用位置偏差信号做硬件触发，兼顾时效性与完整性，最适合本场景。最优选第三种，它避免了长周期盲抓导致的数据淹没，又能锁定故障瞬间前后毫秒级行为。</t>
+          <t>报文抓取分析</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1个异常情况概要：物理层瞬时干扰。具体情况是现场变频器启停时出现零星帧丢失，但无持续误码。解决思路是结合抓包时间戳与产线动作日志比对，确认干扰源时段，在对应物理节点加装屏蔽与滤波措施。1个复杂问题概要：主站任务调度与运动控制周期耦合失配。具体问题是主站周期波动叠加伺服响应延迟，导致位置指令滞后累积。解决思路是抓取主站任务执行时间戳、各轴同步标志位及驱动器实际位置反馈，对比分析时序链路中的最大偏差点，再协同PLC工程师调整任务优先级与同步配置。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>故障诊断与可靠性</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>通信故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>报文抓取分析</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>一台用于精密涂胶的非标设备，其Z轴采用垂直安装的滚珠丝杠配线性导轨结构，在长时间连续运行后出现单向运动重复定位精度下降，而反向运动精度保持良好。已排除控制器参数和编码器误差，且丝杠支撑端轴承无明显游隙。请从丝杠自重变形、导轨预压分布不均及螺母副接触刚度方向性三个角度，解释该单向精度退化现象的形成机理。</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>丝杠垂直安装时，自身重量会使丝杠中段产生向下弯曲变形，导致正向（向下）运动时螺母始终压在丝杠下侧滚道上，长期磨损加剧该侧接触间隙；导轨预压若在单侧偏弱，向下运动时滑块受重力辅助贴合，向上则靠驱动拉起，易因预压不足引发微滑移；螺母副内部滚珠循环路径存在结构不对称，使承载刚度在推/拉方向不一致，向下运动时接触刚度降低，系统弹性变形增大。</t>
+          <t>传动机构理解</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>针对该问题，常用三种现场处置方案：一是调整丝杠支撑方式，加中间托架减小悬臂挠曲，实施快、成本低但需停机改造；二是重新校准导轨预压，用动态测力仪分段检测并局部补偿，精度高但依赖经验与设备；三是更换双向等刚度设计的丝杠螺母副，从根本上解决方向性差异，周期长但长效性最好。综合时效与效果，优先采用支撑优化+导轨预压复核组合方案。</t>
+          <t>丝杠导轨机构</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1个异常情况概要：Z轴向下运动重复定位超差，向上正常；具体情况：设备连续运行8小时后，向下定位标准差增大0.015mm以上，且随温度升高逐步恶化；解决思路：先实测丝杠中点垂向挠度变化趋势，同步检查导轨滑块在上下行程中的预紧手感差异，确认主导因素后再针对性处理。1个复杂问题概要：多因素耦合导致单向精度漂移难以归因；具体问题：丝杠变形、导轨预压衰减、螺母磨损三者在热态下相互影响，无法通过单一参数复位恢复；解决思路：按‘冷态基准建模—热态运动轨迹采样—分方向刚度反演’三步法，用设备自带的伺服电流与位置反馈做间接诊断，锁定主因后再分级干预。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>传动机构理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>丝杠导轨机构</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>请简单说说，在气缸推拉机构里，活塞杆缩回动作主要依靠什么力来完成？</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>活塞杆缩回动作主要依靠压缩空气从有杆腔排出、无杆腔进气所产生的压差推力，配合复位元件（如弹簧或对侧气压）实现。在双作用气缸中，该动作由换向阀切换供气方向后，无杆腔进气推动活塞反向运动；在单作用气缸中，则主要依赖内置弹簧的弹性恢复力。</t>
+          <t>机械执行机构</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>实际工程中常用三种方案：一是双作用气缸配两位五通电磁阀——响应快、控制精准、双向出力稳定，适合高频启停和负载变化大的工况，但需两路气源管路，成本略高；二是单作用弹簧复位气缸配两位三通阀——结构简单、故障点少、断气时自动复位安全，但弹簧力随行程衰减，缩回力小且不可调，不适用于大负载或长行程；三是带缓冲与速放功能的双作用气缸——通过节流阀+快速排气阀组合优化缩回速度与冲击控制，兼顾效率与平稳性，是当前非标设备中最主流的选择。综合来看，双作用气缸配智能节流调节方案适用性最广、可靠性最高。</t>
+          <t>气缸推拉机构</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1个异常情况概要：缩回动作迟滞或不到位。具体情况：气缸有杆腔排气不畅，常见于消声器堵塞、管路弯折过多或换向阀排气口节流过度。解决思路：优先检查排气路径通畅性，用压力表分段测压确认阻滞点，更换高流量消声器并优化管路走向，避免90度直角弯管。1个复杂问题概要：负载存在反向惯性冲击导致缩回末端撞击。具体问题：高速缩回时，被驱动部件因惯性继续前冲，撞击气缸端盖或机械限位，引发异响、定位漂移甚至结构变形。解决思路：在气缸两端加装可调式气缓冲，同时在PLC逻辑中增加缩回末段的速度斜坡降速指令，并结合位置传感器做闭环微调，确保到位前已进入低速缓冲区。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>机械执行机构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>气缸推拉机构</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>请简单说说，视觉定位中常用的图像坐标系到世界坐标系的转换，主要依据什么几何原理？</t>
+          <t>机器视觉应用</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>主要依据刚体变换的几何原理，即在不改变物体形状和尺寸的前提下，通过平移和旋转两个基本操作，把相机拍到的二维图像点，对应到实际产线上工件所在的真实三维空间位置。</t>
+          <t>视觉定位与检测</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>在产线现场，常用三种标定方式：一是单目相机加固定标定板，实施快、成本低，但对安装稳定性要求高，产线振动易导致偏移；二是双目相机直接测距，免标定板，适合动态抓取场景，但对光照变化敏感，金属反光件容易误匹配；三是相机与机器人手眼标定，分眼在手上和眼在手外两种，前者适配协作机器人快速换产，后者更适应传统六轴机械臂，精度高、鲁棒性强，是当前产线主流选择。综合来看，眼在手外的手眼标定方案最稳妥，兼顾精度、重复性和后期维护便利性。</t>
+          <t>视觉定位原理</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1个异常情况概要：标定后定位结果出现系统性偏移。具体情况：同一工件多次拍摄，偏差方向一致且随距离增大而扩大。解决思路：优先检查相机安装支架是否松动或受热变形，再复核标定板放置平面是否与产线基准面平行，最后确认机器人基坐标系是否被意外重置。1个复杂问题概要：多工位共用一套视觉系统时定位一致性下降。具体问题：不同工位因传送带高度、夹具姿态微差，导致同一标定模型在各工位误差不均。解决思路：为每个工位单独保存标定参数组，并在PLC触发信号中嵌入工位标识，由视觉控制器自动加载对应参数，避免人工切换或模型插值带来的累积误差。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>机器视觉应用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>视觉定位与检测</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>视觉定位原理</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>在自动化产线中，视觉系统需要将相机拍摄到的工件图像坐标转换为机器人可执行的物理坐标。请简述实现这一转换时，为何必须先完成相机标定，以及标定过程中最直接影响定位精度的一个关键参数。</t>
+          <t>机器视觉应用</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>因为相机成像存在几何畸变和视角偏差，图像上的像素位置不能直接对应真实空间中的毫米级物理位置；不经过标定，就无法建立图像坐标与物理坐标之间的可靠映射关系，后续所有定位动作都会出现系统性偏移。</t>
+          <t>视觉定位与检测</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>当前产线常用三种标定方式：一是使用高精度二维标定板配合单次静态标定，实施快但对安装刚性要求高；二是多角度多姿态标定，能更好补偿镜头畸变，但耗时较长、需人工干预；三是基于机器人运动轨迹的在线标定，利用机械臂重复定位能力自动采集多组数据，稳定性好且适配产线节拍。综合来看，在线标定方式最适合自动化工程师日常维护场景——它不依赖额外光学设备，复测便捷，且能同步验证相机与机器人坐标系的一致性。</t>
+          <t>视觉定位原理</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1个异常情况概要：标定后定位结果呈现规律性旋转偏移。具体情况：同一工件多次抓取，偏差方向一致且角度固定。解决思路：检查相机安装法兰与机器人末端法兰是否紧固到位，重点排查螺丝松动或垫片变形导致的微倾角变化。1个复杂问题概要：不同工作距离下定位精度波动大。具体问题：工件在传送带前端和后端位置抓取时误差差异明显。解决思路：启用带深度补偿的标定模型，用至少三个不同Z向高度的标定点重新建模，确保整个工作空间内的映射关系均匀有效。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>机器视觉应用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>视觉定位与检测</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>视觉定位原理</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>同一型号工件在不同产线段的视觉检测中，前端工位漏检率偏高而末端工位误检率偏高，两处使用的相机、镜头、光源型号及算法模型完全一致。请分析造成这种空间分布性偏差最可能的三个物理耦合因素，并说明每个因素如何分别影响成像质量与特征稳定性。</t>
+          <t>产线自动化设备实施</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>三个最可能的物理耦合因素是：工件姿态微变、传送带振动累积、环境光干扰梯度。工件姿态微变导致前端成像角度偏离标定基准，降低关键特征对比度，使边缘模糊、纹理弱化；传送带振动在末端段因累积效应加剧，造成图像抖动和运动模糊，破坏像素级定位一致性；环境光干扰梯度指产线不同区段自然光或设备散热光强分布不均，前端易受强反光干扰导致局部过曝，末端则易因光照衰减引发信噪比下降，两者均削弱图像灰度分布的稳定性。</t>
+          <t>视觉检测基础</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>针对这三个因素，常用方案有：一是加装工位级姿态补偿机构，成本低但调节频次高；二是升级传送带张紧与阻尼系统，效果持久但需停线改造；三是部署分区独立光源+遮光罩组合，实施快、适配性强，且能兼顾前端抗反光与末端补光需求，综合时效性与现场可实施性最优。其中分区独立光源方案在新旧产线改造中应用最广，无需动机械结构，调试周期短，对现有节拍影响最小。</t>
+          <t>误检漏检分析</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1个异常情况概要：前端工件表面油膜分布不均。具体情况：前端清洗后残留薄层油膜，在特定入射角下形成干涉色斑，掩盖真实缺陷，导致漏检。解决思路：协同工艺确认清洗干燥时长与风刀角度，同步调整光源入射方向避开敏感反射区。1个复杂问题概要：多工位共用同一光源供电回路。具体问题：末端电压压降导致光源亮度衰减，而前端亮度正常，造成同模型输入图像亮度域偏移。解决思路：为各工位光源配置独立稳压供电支路，并增加亮度闭环反馈模块，实时校准曝光参数。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>产线自动化设备实施</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>视觉检测基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>误检漏检分析</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>在高速包装产线中，视觉系统需每20毫秒向PLC反馈一次定位偏移量，并同步接收PLC发出的触发信号与当前工位状态字；若现场已部署工业以太网，但PLC侧仅开放有限的实时通信资源，你会如何设计视觉与PLC间的双向数据交互架构？请简述核心选型依据及避免扫描周期抖动的关键控制逻辑。</t>
+          <t>机器视觉应用</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>必须采用确定性高的周期性数据交换方式，视觉侧主动按固定20毫秒节奏发起数据同步，PLC侧不依赖自身扫描周期被动响应，而是由视觉系统主导时序；所有交互数据须压缩在单次通信帧内完成读写，避免分多次握手。</t>
+          <t>视觉系统集成</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是用PLC原生支持的轻量级实时协议，由视觉端模拟主站轮询，时序可控但受PLC资源配额限制；二是通过PLC的专用I/O映射区共享内存式交互，视觉直接读写指定地址，延迟最低且不占通信通道，但需提前协调地址规划和数据格式；三是加装边缘通信网关做协议桥接，增加冗余但引入额外抖动。综合来看，优先选用I/O映射区方式，它不新增网络负载、响应稳定、适配现有工业以太网物理层，最契合产线对确定性和资源约束的双重要求。</t>
+          <t>视觉与PLC交互方式</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1个异常情况概要：视觉触发信号偶发丢失。具体情况：PLC输出触发沿过窄或存在电气噪声，导致视觉端未能可靠捕获上升沿。解决思路：在视觉端启用硬件消抖+可配置触发窗，同时要求电气侧检查输出回路阻抗匹配与屏蔽接地。1个复杂问题概要：多工位状态字与偏移量时间戳错位。具体问题：PLC状态更新与视觉采样不同步，导致反馈的偏移量对应错误工位。解决思路：视觉系统以接收到的PLC触发信号为唯一采样基准，所有计算和打包均绑定该时刻，PLC侧同步固化触发与状态更新的时序关系，双方不做独立计时。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>机器视觉应用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>视觉系统集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>视觉与PLC交互方式</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>请简单说说，自动化导入项目中，‘设备折旧费用’属于投资成本还是运营成本？</t>
+          <t>方案可行性与立项</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>设备折旧费用属于投资成本。它反映的是自动化设备购置后，在使用年限内分摊的初始投入价值，本质是前期资本性支出的会计转化，不随当期生产量或运行时长实时变动。</t>
+          <t>需求分析与可行性评估</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>在制造业自动化导入的可行性评估中，常见有三种处理方式：一是按直线法在立项阶段一次性计入总投资额，优势是口径统一、便于快速比对ROI；二是按实际使用年限与产能利用率动态调整折旧周期，更贴近产线真实负荷，但需跨部门协同确认产能数据；三是将折旧单列但绑定设备全生命周期维护预算，强化投资与运维的联动性。综合来看，第一种最常用——既符合财务立项规范，又契合工程师在方案阶段聚焦‘投入-产出’主逻辑的工作习惯，时效性强且无需依赖后期运行数据。</t>
+          <t>自动化导入投资回报判断</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1个异常情况概要：设备提前报废导致原定折旧周期失效；具体情况：产线工艺升级后，新导入的视觉检测设备仅用18个月即被替代；解决思路：立项时同步识别技术迭代风险，在投资估算中设置折旧弹性区间，并约定设备处置残值回收机制。1个复杂问题概要：同一台设备在多个自动化项目中复用；具体问题：某PLC控制器先用于焊接单元，后调至装配线，其折旧应归属哪个项目；解决思路：以设备首次投入量产使用的项目为折旧归属主体，后续调拨按内部资产划转处理，避免重复分摊或漏计，确保各项目投资回报测算边界清晰。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>方案可行性与立项</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>需求分析与可行性评估</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>自动化导入投资回报判断</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>请简述在自动化导入可行性评估中，‘年均节约金额’一般由哪些时间维度的数据得出？</t>
+          <t>方案可行性与立项</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>年均节约金额主要依据过去12个月的实际运行数据、未来12个月的预测运营数据，以及项目实施后首年完整周期的模拟测算数据这三类时间维度的数据综合得出。</t>
+          <t>需求分析与可行性评估</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>实际运行数据通常取最近连续12个月的生产记录，优势是真实可靠、无需假设，但缺点是可能受季节性波动或临时工况干扰；预测运营数据基于当前产线节拍、良率、人工排班等参数推演，时效性强、响应快，但依赖输入参数准确性；模拟测算数据则结合设备停机记录、换型频次、能耗实测等现场采集信息建模生成，覆盖维度最全、贴近落地场景，虽需现场协同采集，但能有效规避历史异常干扰，是制造业自动化工程师开展立项评估时最常用且最稳妥的方法。</t>
+          <t>自动化导入投资回报判断</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1个异常情况概要：历史12个月数据中存在停产检修或订单断档导致人工工时大幅偏低。具体情况：该时段人工成本被严重低估，直接套用将高估节约金额。解决思路：剔除非正常运营月份，替换为同产线同类产品稳定生产期的加权均值。1个复杂问题概要：多班次、多型号混线生产下人工成本与设备投入难以单一分摊。具体问题：不同型号切换频繁，单台设备对应的人工节省无法按台套归集。解决思路：以标准工时为锚点，按各型号实际作业占比反向拆分人工节省量，再叠加设备运行效率提升带来的间接节省，形成可验证的分项节约结构。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>方案可行性与立项</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>需求分析与可行性评估</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>自动化导入投资回报判断</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>在规划一条自动化产线的整体方案时，如果上游来料的节拍是每分钟12件，而下游工序要求每分钟处理15件，你在构思设备整体布局时会优先考虑哪些关键因素来协调这个节拍差异？请简述。</t>
+          <t>方案可行性与立项</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>需优先考虑缓冲区设置、工序拆分可能性、设备并行配置能力以及产线柔性响应边界这四个关键因素。</t>
+          <t>方案设计与布局规划</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>常见协调方式有四种：一是增设缓存输送单元，优势是实施快、风险低，但占用空间大且无法根本解决产能缺口；二是将下游工序拆解为两道并行工位，优势是节拍匹配稳定、利用率高，但对工艺可分性要求严、布局复杂度上升；三是上游增加预处理缓存+节拍提升模块，优势是源头协同性强，但改造成本高、依赖供应商配合；四是采用动态调度式柔性输送系统，优势是适应多品种小批量变化，但对控制系统集成能力要求高。综合来看，在立项阶段最推荐第二种——工序拆分并行化，因其在可行性、投资回报和后期运维之间平衡性最好。</t>
+          <t>设备整体方案构思</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1个异常情况概要：上游实际来料波动远超预期，导致缓冲区频繁溢出或抽空；具体情况：来料节拍在8～16件/分钟间无规律跳变；解决思路：在方案中预留可扩展的缓存容量接口，并约定上游提供基础节拍稳定性承诺条款，作为立项前置条件。1个复杂问题概要：下游工序存在不可拆分的核心工艺步骤；具体问题：该步骤必须单机连续完成，无法物理并行；解决思路：回归节拍瓶颈分析，联合工艺部门验证是否可通过优化单次循环动作（如缩短等待、重叠辅助时间）提升单机效率，将方案可行性评估前移至立项评审环节。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>方案可行性与立项</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>方案设计与布局规划</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>设备整体方案构思</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>某工业阀门产线拟以视觉引导机器人替代人工完成阀体密封面缺陷复检，原人工复检漏检率为1.8%，新方案理论识别率达99.2%，但需持续采集新批次毛坯图像用于模型迭代，且现场压缩空气含油量超标可能影响镜头寿命。请简述你如何量化评估该自动化方案中‘识别能力提升’与‘运维不确定性上升’之间的净收益边界，并说明关键折损项的测算逻辑。</t>
+          <t>方案可行性与立项</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>作为自动化工程师，我首先明确：净收益边界不是技术指标差值，而是从产线实际运行视角出发，对比人工复检失效带来的质量损失成本，与新方案引入后新增的运维成本、停机风险、模型维护投入之间的动态平衡点。</t>
+          <t>需求分析与可行性评估</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>常用评估路径有三种：一是基于历史质量数据回溯法，用近半年同型号阀体售后索赔、返工、报废金额反推漏检实际损失；二是产线级故障树映射法，把漏检导致的下游装配失效、客户投诉等环节转化为单件质量成本；三是运维压力模拟法，通过现场实测压缩空气含油量对镜头清洁周期的影响，结合模型迭代频次预估年度非计划停机时长。其中，故障树映射法最实用——它不依赖理想化识别率，而是紧扣产线真实失效链路，时效性强、数据可得性高，且能自然融入现有质量成本核算体系。</t>
+          <t>自动化导入投资回报判断</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1个异常情况概要：模型迭代滞后于毛坯工艺变更。具体情况：新批次毛坯铸造纹理变化未及时触发图像采集，导致识别率在两周内骤降至92%以下。解决思路：将图像采集动作与车间MES的批次开工指令强关联，设置自动触发+人工复核双校验机制。1个复杂问题概要：压缩空气含油引发的镜头寿命波动掩盖真实识别衰减。具体问题：镜头模糊导致误判增多，但被误归因为模型不准，反复调参延误根本处置。解决思路：在视觉系统前端加装光学透射率实时监测模块，当透射率下降超阈值时，自动锁定模型参数并推送‘疑似光学污染’告警，强制进入设备维保流程而非算法优化流程。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>方案可行性与立项</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>需求分析与可行性评估</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>自动化导入投资回报判断</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>请简述在评估自动化方案可行性时，为什么需要确认被控设备的供电电压规格？</t>
+          <t>智能制造改善</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>因为供电电压规格直接决定现场电气接口能否匹配、控制信号能否可靠驱动执行机构，是判断方案能否落地实施的基础前提。</t>
+          <t>自动化方案评估</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>常见处理方式有三种：一是沿用原有供电系统，优势是改造成本低、周期短，但可能受限于老旧设备兼容性或容量裕度不足；二是加装专用电源模块，适配性好、稳定性高，但会增加布线复杂度和故障点；三是整体更换配电单元，适用于产线升级场景，长期可靠性最优，但涉及停产协调与投资审批。综合来看，在产线不停机前提下，优先采用模块化电源适配方案，兼顾时效性、安全性和可验证性。</t>
+          <t>方案可行性判断</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1个异常情况概要：现场实测电压与铭牌标称值偏差超限。具体情况：老旧产线中因线路老化、负载不均导致实际供给电压低于设备最低工作阈值，造成气动阀响应迟滞或伺服启停失败。解决思路：在方案评估阶段即要求提供近三个月配电柜出线端实测记录，并同步安排现场电压波动摸底测试，将结果纳入可行性否决项。1个复杂问题概要：多品牌设备混用导致供电制式冲突。具体问题：新旧产线并存时，部分进口设备要求单相220V交流，而国产PLC扩展模块默认支持三相380V直流供电，存在接口不可桥接风险。解决思路：在方案设计初期组织跨供应商联合确认会，明确统一供电架构层级（如统一采用隔离型宽压输入模块），并以实物接口联调报告作为可行性闭环依据。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>智能制造改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>自动化方案评估</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>方案可行性判断</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>请简述单机调试阶段设备的动作指令由谁发出，联机调试阶段通常由谁统一协调。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>单机调试阶段，设备的动作指令由自动化工程师本人直接发出；联机调试阶段，通常由自动化工程师统一协调。</t>
+          <t>设备调试</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>在实际工作中，单机调试时工程师通过手持操作盒、HMI临时界面或PLC编程软件的手动模式下发指令，确保设备本体功能正常；联机调试时，协调方式主要有三种：一是由主控PLC程序逻辑自动触发各设备动作，工程师负责监控和干预；二是由中控HMI作为统一操作入口，工程师通过权限分级操作；三是在多专业交叉场景下，由自动化工程师牵头组织电气、机械、工艺人员联合确认动作时序。第一种效率最高、稳定性最好，适用于产线逻辑清晰的场景；第二种人机交互更直观，便于跨岗位协同；第三种虽耗时但风险可控，常用于新产线首台套调试。综合来看，以主控PLC逻辑驱动为主、工程师实时盯控为辅的方式最常用且时效性与可靠性兼顾。</t>
+          <t>单机与联机调试区别</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1个异常情况概要：单机调试时设备响应指令但动作异常。具体情况：比如电机转动方向反、气缸伸出缩回逻辑颠倒、安全门未闭合却允许启动。解决思路：立即切回手动模式，核对IO信号实际状态与图纸一致性，重点检查传感器安装方向、阀岛接线极性、伺服使能/方向信号定义是否与程序约定一致，不依赖程序注释，以现场实测信号为准。1个复杂问题概要：联机调试中多个设备动作不同步或时序紊乱。具体问题：输送线已到位，但机械手未抓取，或AGV到达工位后焊接机器人未同步启动。解决思路：暂停全线运行，回溯主控PLC中各设备触发条件的使能链路，逐级验证前序完成信号是否真实反馈、有无滤波延迟或信号抖动，同时确认各子站通信响应时间是否在设计裕度内，必要时插入诊断标记点辅助定位瓶颈环节。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>设备调试</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>单机与联机调试区别</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>在对一台新安装的PLC控制的装配工位进行上电前检查时，发现现场传感器的供电电源与PLC输入模块共用同一组直流24V电源，且该电源输出端未加装保险丝。请简述这一配置可能带来的主要风险，以及应如何规范处理。</t>
+          <t>现场调试与验收</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>这种共用电源且无保险丝的配置，会使传感器短路或过载时直接冲击PLC输入模块，导致模块损坏；同时一旦电源异常，整个输入回路将同时失电，造成信号丢失、误判甚至停机，违反上电前检查中‘电源隔离与保护完备性’的基本要求。</t>
+          <t>单机调试</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>常见处理方式有三种：一是为传感器单独配一路带保险的24V电源，隔离性好但增加布线和成本；二是用同一电源但为传感器支路单独加装微型断路器或自恢复保险，响应快、易实施，是当前主流做法；三是依赖PLC模块自带过流保护，但实际多数输入模块仅限短时耐受，不能替代前端保护。综合时效性、可靠性与现场可操作性，第二种方案最合理，既满足规范又便于调试阶段快速整改。</t>
+          <t>上电前检查</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1个异常情况概要：传感器线缆破损引发间歇性短路。具体情况：压接不牢或拖链磨损导致正负极瞬时碰触，电源电压跌落并反复冲击PLC输入点。解决思路：上电前必须分路测量绝缘电阻，并对活动电缆段做弯折测试，确认无隐性短路风险后再通电。1个复杂问题概要：多类型传感器混接导致共模干扰加剧。具体问题：光电、接近、编码器等不同原理传感器共用电源时，开关噪声叠加，使PLC采集到跳变信号。解决思路：按信号敏感度分组供电，关键输入通道优先使用独立稳压电源，并在电源出口加装π型滤波，调试时用示波器抓取电源纹波验证有效性。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>现场调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>单机调试</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>上电前检查</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>某包装设备在连续运行两小时后，PLC输出模块控制的多个电磁阀陆续出现响应延迟，而输入信号和程序逻辑均无异常。请简述你如何通过观察现场现象和基础诊断手段，快速区分是输出模块老化、电源波动还是接线接触不良导致的该类渐进式故障。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>先确认故障是否随运行时间推移逐步加重，再同步观察所有受影响电磁阀的动作一致性：若全部延迟程度相近且同步恶化，倾向输出模块或公共电源问题；若各阀延迟起始时间、严重程度不一致，则更可能是单点接线问题。</t>
+          <t>故障诊断</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>用万用表在设备带载运行中实测输出端子电压——若电压随时间持续下降，指向电源或模块供电回路异常；若电压正常但电磁阀动作滞后，重点查模块输出驱动能力衰减；若仅个别通道电压跳变或偏低，配合晃动接线端子观察动作变化，可快速锁定虚接点。三种方法中，带载电压测量最直接高效，兼顾时效性与覆盖性，无需停机拆件，且能一次判断电源、模块、接线三类主因。</t>
+          <t>故障定位思路</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1个异常情况概要：输出模块表面无烧痕、无报警，但带载后端子压降明显增大。具体情况：模块散热不良导致内部驱动晶体管热态导通电阻上升，表现为冷态正常、热态输出延迟。解决思路：在设备运行一小时后立即测量各输出通道对地电压及负载电流，对比冷热态差异，结合模块温升判断老化程度。1个复杂问题概要：同一输出模块下部分通道异常，其余正常，但更换模块后故障转移至新模块对应通道。具体情况：实际是底板插槽氧化或背板供电走线局部老化，造成接触阻抗随温升增大。解决思路：不急于换模块，先清洁插槽并测量背板供电电压在热态下的纹波与跌落幅度，确认是否为安装结构层问题。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>故障定位思路</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>一条焊接机器人工作站频繁在焊缝收弧阶段触发电流异常中断，示教器未报错，焊机通信日志显示指令完整下发。请简述你如何利用PLC与焊机间过程数据帧的时序完整性、送丝机构响应延迟的温度依赖性、以及电弧电压采样回路的共模干扰抑制能力，构建故障定位逻辑链。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>我会先确认PLC向焊机发送的过程数据帧在收弧时刻是否严格满足时序要求，比如关键参数更新是否滞后于焊机内部状态切换；再检查送丝电机在连续作业升温后，实际送丝速度是否比设定值慢，导致收弧阶段熔池填充不足；最后验证电弧电压采样环节在高dv/dt工况下，能否有效抑制来自变频器或主回路的共模干扰，避免误判熄弧。</t>
+          <t>故障诊断</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>常用方法有三种：一是用高速逻辑分析仪抓取PLC与焊机间的实时过程帧，看收弧指令与电流闭环响应是否存在时间偏移；二是通过红外测温配合送丝电流闭环测试，量化不同温区下的响应延迟变化；三是用差分探头实测采样端口共模电压幅值，并对比滤波器投入前后的电压跳变稳定性。第一种时效性最好但需协议支持，第二种覆盖全面但耗时较长，第三种定位精准且复现性强，综合来看优先采用第三种结合第一种交叉验证。</t>
+          <t>故障定位思路</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1个异常情况概要：送丝机构热漂移导致收弧瞬时送丝量不足；具体情况：连续焊接后电机绕组温升使堵转扭矩下降，相同控制电流下出丝力减弱；解决思路：在PLC侧增加基于累计焊接时长和环境温度的送丝补偿系数，并设置收弧前0.5秒的预提速窗口。1个复杂问题概要：共模干扰在收弧瞬态叠加于电压采样回路引发虚假熄弧判定；具体问题：焊机主回路关断瞬间产生高频传导干扰，经采样线缆耦合进入ADC前端；解决思路：现场加装共模扼流圈+单点接地优化，并在PLC中启用电压信号滑动中值滤波与变化率门限双重判据。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>故障定位思路</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>一条装配线上的视觉定位系统在更换同型号新相机后，首次标定合格，但连续运行48小时后重复定位精度下降超限，且仅在特定工件节拍下发生。请简述你将如何构建可复现的触发条件组合，并说明为何必须同步控制环境温度、供电纹波与运动触发时序这三个变量才能完成有效故障验证。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>首先明确触发条件组合必须包含三个刚性要素：连续运行时长（≥48小时）、目标工件节拍（精确复现异常发生的周期值）、以及相机通电起始状态（从冷机上电开始计时）。这三个要素缺一不可，否则无法稳定复现故障。</t>
+          <t>故障诊断</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>常用方法有四种：一是全工况循环法，按产线最大节拍连续跑满72小时，覆盖热积累全过程，但耗时长、干扰多；二是阶梯升温+节拍扫描法，分段提升环境温度并逐档测试各节拍点，效率高但易漏掉温度与节拍耦合点；三是时序注入法，在PLC程序中嵌入可控延时模块精准复现触发时刻，对编程能力要求高；四是三变量联动记录法，用数据采集模块同步记录温升曲线、电源电压波动频谱和触发信号边沿抖动，再回放重构。综合来看，第三种加第四种组合最优——既保证时序精度，又保留物理变量真实响应，兼顾时效性与可追溯性。</t>
+          <t>故障复现与验证</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1个异常情况概要：温漂引发镜头焦距微变。具体情况：相机外壳热胀导致镜头与图像传感器相对位移，仅在高速节拍下因曝光窗口窄而放大误差。解决思路：在相机安装结构中增加低膨胀系数垫片，并在标定流程中增加热平衡后二次校验环节。1个复杂问题概要：供电纹波与运动触发存在相位敏感性。具体问题：当伺服启停瞬间的电流冲击恰好叠加在相机曝光前10毫秒内，造成CMOS模拟前端供电瞬降，导致像素响应非线性。解决思路：将相机供电与伺服动力电源物理隔离，同时在PLC触发输出端增加可调延迟补偿，使曝光时刻避开电流尖峰窗口。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>故障复现与验证</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>在PLC顺序控制设计中，‘先启后停’类动作对互锁条件有什么基本要求？</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>必须确保启动信号生效时，停止信号被强制屏蔽；只有当启动动作完全执行完毕、运行状态稳定建立后，停止信号才被允许参与逻辑判断。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>常见实现方式有三种：一是用步进指令配合状态位锁存，优点是逻辑清晰、便于调试，但对程序员状态建模能力要求高；二是用置位复位指令构建双稳态，响应快、资源占用少，但若复位条件设计不当易导致状态悬空；三是用带使能端的自保持回路，结构简单、兼容性强，但需额外校验使能链路完整性。综合来看，第三种更适合制造业现场快速部署与维护，兼顾可靠性与可读性。</t>
+          <t>动作条件互锁</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1个异常情况概要：启动过程中突发急停触发，但停止信号未及时生效。具体情况：因互锁逻辑将停止条件挂在启动完成之后，导致急停信号被延迟响应。解决思路：将急停作为最高优先级硬线接入PLC急停输入点，绕过所有软件互锁，在硬件层直接切断输出回路。1个复杂问题概要：多设备协同下的‘先启后停’级联失效。具体问题：上游设备刚启动、下游设备已发出停止请求，造成逻辑冲突和机械干涉。解决思路：引入统一的流程使能标志，由主控步序集中管理各设备启停使能窗口，并设置最小启动保持时间阈值，确保动作时序留有工艺余量。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>动作条件互锁</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>请简单说说PLC顺序控制里，‘急停信号触发后立即终止当前步’这一要求，体现了哪种异常中断处理原则？</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>这体现了‘最高优先级强制响应’的异常中断处理原则——即当危及人身或设备安全的紧急信号出现时，系统必须无条件、无延时地中断当前所有运行逻辑，进入预设的安全状态。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>在实际产线调试中，主要有三种实现方式：一是用PLC的硬件中断输入直接驱动安全输出回路，响应最快但灵活性低；二是通过扫描周期内首段程序强制清空步进标志并跳转至安全步，兼顾可靠性和可维护性；三是采用专用安全控制器协同管理，适合高风险场景但成本高。综合来看，第二种方式在制造业产线中应用最广——它既满足安全响应时效要求（通常在100毫秒内完成步终止），又便于工程师在线修改、验证和归档，符合自动化工程师日常维护与迭代的实际工作节奏。</t>
+          <t>异常中断处理</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停信号抖动导致重复触发。具体情况：现场按钮触点老化或接线松动，造成信号频繁通断，使PLC误判多次急停，引发反复启停和定位偏差。解决思路：在信号采集端加入硬件滤波，并在PLC程序中设置不小于20毫秒的软件去抖确认窗口，且仅在首次有效边沿执行终止动作。1个复杂问题概要：多工位协同流程中局部急停影响全局状态一致性。具体问题：某装配工位触发急停后，上下游工序仍在运行或缓存数据未同步清除，导致复位后逻辑错乱。解决思路：设计分层安全状态机，急停触发时不仅终止本步，还向关联工位广播‘暂停等待’指令，并统一由主控步协调各单元进入可复位的安全挂起态，确保重启前状态全量对齐。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>异常中断处理</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>在一条装配线上，当机械手完成抓取动作后，传送带才允许启动；同时如果安全光幕被遮挡，传送带必须立即停止。请简述这两个条件之间是如何通过PLC程序实现互锁保护的。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>这是典型的顺序控制中动作条件互锁：传送带的启动必须同时满足两个前提——机械手已发出‘抓取完成’信号，且安全光幕处于未遮挡状态；而传送带运行中任一时刻，只要光幕被遮挡，就必须无条件切断输出，强制停机。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>实际工程中常用三种互锁实现方式：一是将光幕信号作为传送带输出回路的硬件急停串联点，响应最快但灵活性低；二是用PLC内部逻辑做双重判断——启动时做‘与’门校验，运行中做‘或’门中断，兼顾安全与可调试性；三是引入安全PLC模块独立处理光幕信号，再与主PLC通信协同，适合高风险场景。综合来看，第二种方式在制造业产线中应用最广，它既满足功能安全基本要求，又便于现场排查和工艺调整，无需额外安全认证成本。</t>
+          <t>动作条件互锁</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1个异常情况概要：光幕信号偶发抖动导致传送带误停。具体情况：光电开关受粉尘或振动影响产生瞬时通断，PLC未加滤波直接采样，触发误停。解决思路：在PLC输入端配置可调时间滤波（如10～30毫秒），并结合信号边沿检测逻辑，只响应持续有效的遮挡状态。1个复杂问题概要：机械手与传送带动作时序存在临界竞争。具体问题：机械手刚发出抓取完成信号，但末端尚未完全撤离光幕区域，此时若传送带立即启动，可能造成干涉。解决思路：在PLC程序中插入‘安全等待窗口’，即收到抓取完成信号后，延时确认光幕连续无遮挡至少200毫秒，再开放传送带启动权限，形成时间维度上的双重确认。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>动作条件互锁</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>在冲压设备的顺序控制中，滑块下行前必须确保防护门已关闭且双手按钮同时按下；若其中任一信号丢失，下行动作应立即终止并锁定。请简述这一设计中互锁机制的核心作用。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>互锁机制的核心作用是强制约束动作执行的前提条件，确保只有当所有安全条件同时满足时，危险动作才被允许启动；一旦任一条件失效，系统必须无延迟地中断当前动作并阻止再次触发，从而把人员伤害风险控制在物理和逻辑双重可信赖的边界内。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>当前主流有三种实现方式：一是硬件硬接线互锁，响应最快但扩展性差、故障定位难；二是PLC内部逻辑双回路互锁，兼顾响应速度与可维护性，支持条件动态配置；三是安全控制器+安全输入模块方案，符合功能安全等级要求，但成本高、调试周期长。综合时效性、可靠性与产线落地成熟度，PLC内部双通道独立扫描+输出自锁的逻辑互锁是最常用且最平衡的选择。</t>
+          <t>动作条件互锁</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1个异常情况概要：防护门微动开关接触不良导致信号偶发丢失。具体情况：门体闭合到位但触点氧化造成瞬时断开，PLC误判为门未关而急停滑块，引发频繁停机。解决思路：在逻辑中加入短时滤波与状态保持机制，同时设置信号质量诊断报警，不直接中断动作，而是预警并限制连续触发次数。1个复杂问题概要：双手按钮存在人为‘搭桥’操作风险。具体问题：操作员用工具同时压住两个按钮，绕过双手操作意图，使互锁形同虚设。解决思路：引入按钮按下时序差检测与压力持续时间验证，并配合安全光幕或区域扫描做冗余行为判断，从动作意图层面强化互锁有效性。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>动作条件互锁</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>请简单说说：当PLC处于手动模式时，自动控制逻辑应处于什么状态？</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>自动控制逻辑应完全停止执行，不触发任何输出动作，也不参与过程判断和连锁响应。</t>
+          <t>PLC程序结构</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>实际工程中主要有三种处理方式：一是用主使能标志位全局屏蔽自动逻辑，优点是结构清晰、调试方便，但需确保所有自动分支都受控于该标志；二是对每段自动逻辑单独加模式判断条件，灵活性高，但易遗漏分支，维护成本上升；三是通过状态机跳转强制进入手动专属分支，安全性好，但要求程序有统一的状态管理架构。综合来看，主使能标志位方式在制造业产线项目中最常用，它兼顾开发效率、可读性和现场验证便捷性，尤其适合多班组协作、快速投产的场景。</t>
+          <t>手自动模式切换</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1个异常情况概要：手动模式下自动逻辑意外触发输出。具体情况：操作员切入手动后，某台泵仍按原设定周期启停。解决思路：核查主使能标志是否被其他逻辑复位或覆盖，重点检查急停恢复、模式切换沿触发、以及跨OB块的数据传递是否同步。1个复杂问题概要：手自动切换瞬间出现设备误动作。具体问题：模式切换帧内，自动逻辑最后一周期输出与手动指令产生竞争。解决思路：采用双稳态锁存+切换延时确认机制，在模式变更后等待一个完整扫描周期再更新使能状态，并在HMI侧增加切换成功反馈确认环节。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PLC程序结构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>手自动模式切换</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>一条多工位注塑机辅机联动系统中，机械手取件动作仅在合模完成、冷却时间到且顶针完全退回后才被允许；但顶针若开始伸出，机械手必须立即中止所有移动指令。请简单说说，这类存在时序先后与即时阻断双重要求的场景，PLC顺序控制中的动作条件互锁应如何分层设置，以兼顾安全性与流程连续性。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>应将互锁逻辑分为两级：一级是启动许可条件，即三个静态前提必须全部满足才能使能取件动作；二级是运行中强制中断条件，即顶针伸出信号一旦出现，无论当前处于什么阶段，都必须无延迟切断所有运动输出。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>常见做法有三种：一是纯软互锁，在主程序中用置位复位配合常闭触点串联中断逻辑，响应快但依赖扫描周期；二是硬件硬接线急停链路直切伺服使能，安全等级高但灵活性差；三是混合式——用PLC高速中断指令捕获顶针伸出沿信号，触发独立安全任务块执行急停输出，同时主流程保留完整时序判断。第三种最常用，既满足ISO 13849 PL e级响应要求，又不牺牲工艺节拍稳定性。</t>
+          <t>动作条件互锁</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1个异常情况概要：顶针位置传感器信号抖动导致误触发中断。具体情况：接近开关受油污或振动影响产生瞬时通断，引发机械手频繁急停。解决思路：在PLC输入端加50毫秒硬件滤波，并在软件中做边沿确认+双周期验证，只对持续稳定的伸出信号生效。1个复杂问题概要：多工位同步下顶针状态与机械手动作存在跨站时序耦合。具体问题：某工位顶针未退到位，但相邻工位已进入取件准备，主流程易因全局等待降低效率。解决思路：采用工位级独立互锁+中央协调标志位机制，各工位自判本位条件，仅在跨工位资源争用时由主控站统一仲裁，避免单点阻塞整线。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>动作条件互锁</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>在伺服回零逻辑中，'减速挡块触发后继续寻找原点信号'这一过程，主要目的是保证什么？</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>保证回零动作的重复定位精度和工艺基准可靠性。</t>
+          <t>运动控制调试</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>这个过程常用三种实现方式：一是靠硬件限位开关配合编码器Z相信号，响应快但机械磨损影响长期稳定性；二是仅依赖伺服驱动器内部Z相捕捉，抗干扰弱，易受电机抖动或信号毛刺误触发；三是PLC侧双沿判别+软件滤波，兼顾鲁棒性和可调性，支持现场微调滤波窗口和边沿确认逻辑，是当前产线调试中最主流、最稳妥的选择。</t>
+          <t>伺服回零逻辑</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1个异常情况概要：减速挡块触发后长时间未捕获到原点信号。具体情况：可能因编码器Z相接线松动、光电开关灵敏度衰减，或电机低速爬行阶段存在轻微反向晃动导致Z相错过。解决思路：先确认挡块到位后伺服是否真正进入低速搜寻模式，再分段验证Z相信号电平质量与PLC输入滤波设置是否匹配，最后用示波器抓取实际信号波形比对。1个复杂问题概要：多轴协同回零时，某轴因原点信号偶发丢失导致整机停机。具体问题：并非单轴故障，而是主站PLC在等待该轴原点反馈超时后主动终止同步流程，暴露出回零状态机缺乏降级处理机制。解决思路：在PLC程序中为每轴增设‘准原点’临时标记位，当Z相连续三次在预期窗口内出现时即允许进入后续动作，并同步触发报警而非急停，保障产线柔性恢复能力。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>运动控制调试</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>伺服回零逻辑</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>某食品包装产线需检测高速运行（300包/分钟）的金属托盘是否到位，但传送带振动大、环境湿度高，且托盘材质在不同批次中存在不锈钢、铝和镀层钢三种类型。请简述在此多变工况下，如何依据传感器选型原则系统性确定最适配的检测方案。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>需紧扣传感器选型四大核心原则：检测对象特性适配性、工况环境适应性、响应速度匹配性、输出信号兼容性。其中对象特性指金属种类差异带来的导磁性与电导率变化；工况环境包括高湿、强振；响应速度须满足单包检测周期≤200毫秒；信号需能直接接入产线PLC数字输入模块。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>常见方案有三类：一是电感式传感器，对不锈钢响应强但铝和镀层钢易漏检，抗振好但湿度高时易结露误动；二是电容式传感器，可覆盖所有金属类型，但受湿度影响大，需频繁校准；三是双频涡流传感器，通过切换激励频率自动适配不同材质，抗湿抗振能力强，响应快，现场调试一次即可适配全批次。综合来看，双频涡流方案最适配——它不改变硬件安装，仅通过参数配置应对材质切换，符合自动化工程师‘一次部署、多态适配’的工程实践要求。</t>
+          <t>传感器选型原则</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1个异常情况概要：传感器在高湿环境下持续误触发。具体情况：冷凝水附着探头表面，导致电容或电感信号漂移。解决思路：选用IP69K防护等级、带疏水涂层探头，并在PLC程序中加入300毫秒防抖滤波，而非单纯调高阈值。1个复杂问题概要：同一条产线切换托盘材质时检测稳定性骤降。具体问题：不同金属对磁场扰动幅度差异超2倍，单一灵敏度无法兼顾。解决思路：在HMI设置材质模式快捷切换按钮，联动PLC自动加载对应传感器增益与判定阈值，实现工艺参数与传感参数同步联动。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>传感器选型原则</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>某老旧设备升级时，原位移传感器输出为1-5V标准信号，新控制器仅支持RS-485数字接口。请简述你在不更换传感器的前提下，如何实现信号兼容，并解释不同转换方案对测量精度和抗干扰能力的影响。</t>
+          <t>自动化设备基础</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>位移传感器输出1-5V是模拟电压信号，本质是连续变化的物理量表征；而RS-485是数字通信接口，传输的是离散编码后的数据帧。二者属于不同信号类型，不能直连，必须通过模数转换与协议适配环节建立连接。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>常见方案有三种：第一种是用带模拟输入和RS-485输出的智能信号变送器，它内置高精度ADC和隔离电路，能直接读取1-5V、线性转换并打包成标准数据帧发送，精度高、抗干扰强，适合产线长期运行；第二种是加装PLC的模拟量输入模块再通过其RS-485口转发，灵活性好但链路长、多一次转换易引入累积误差；第三种是用通用数据采集器加定制固件，成本低但调试周期长、现场维护难。综合看，智能变送器方案最稳妥，既满足产线快速改造需求，又兼顾精度与抗干扰稳定性。</t>
+          <t>传感器信号输出类型区别</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1个异常情况概要：现场出现测量值跳变或零漂。具体情况：变送器供电波动或接地不良导致模拟前端共模干扰抬升。解决思路：检查变送器独立供电质量，确认信号地与控制器地单点连接，必要时加装DC-DC隔离电源。1个复杂问题概要：多台同类传感器共用同一RS-485总线时通信冲突或丢数。具体问题：未配置唯一地址或波特率不一致，导致控制器无法区分来源。解决思路：逐台上电单独设置设备地址与通信参数，用示波器抓取总线波形验证信号完整性，确保终端电阻匹配到位。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>自动化设备基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>传感器信号输出类型区别</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>请简单说说漫反射式光电传感器的检测距离和安装高度之间有什么基本规律？</t>
+          <t>自动化设备基础</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>漫反射式光电传感器的检测距离，会随着安装高度的增加而明显缩短；安装越低，有效检测距离越接近标称值；安装越高，光束发散和目标反射衰减加剧，实际可稳定检测的距离就越小。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>在产线部署中，常用三种调整方式：一是固定支架微调高度，优点是结构简单、抗振性好，但调节范围窄、不适应多型号切换；二是加装可调角度的万向节支架，能兼顾高度与入射角，但长期运行易松动导致误检；三是配合背景抑制型传感器使用，通过内置算法区分目标与远背景，对高度变化容忍度高，稳定性最好，已成为当前主流产线选型方案。</t>
+          <t>检测距离与安装边界</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1个异常情况概要：传感器在额定高度安装后，突然出现间歇性无信号。具体情况：产线更换了反光率更低的工件材质，原有高度下反射光强已低于可靠触发阈值。解决思路：先用示教功能重设灵敏度，再微降安装高度5～10毫米并做重复性验证。1个复杂问题概要：同一工位需兼容金属与塑料两种工件，反射特性差异大，无法用单一高度兼顾检测可靠性。具体问题：调低高度虽保住了塑料件检测，但金属件易因过强反射造成饱和误动作。解决思路：采用双阈值模式传感器，分别设定高低反射率工件的独立触发区间，并通过PLC信号切换工作档位，实现一机两用。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>自动化设备基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>检测距离与安装边界</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>请简单说说为什么急停回路需要独立于主控制系统供电。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>因为急停功能必须在主控制系统完全失效时仍能可靠动作，独立供电能确保即使PLC断电、程序崩溃或通信中断，急停回路依然具备能量驱动安全输出元件，从而切断动力源。</t>
+          <t>安全回路设计</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>目前主流有三种实现方式：一是用专用安全继电器配独立电源，响应快、认证齐全，但成本高、扩展性弱；二是采用带安全输入的模块化安全控制器，集成诊断和冗余检测，调试稍复杂但后期维护便利；三是用双通道硬接线+独立直流电源直驱安全接触器，结构最简、故障率最低，适合产线改造类项目。综合来看，第三种在制造业产线现场应用最广——它不依赖软件逻辑，抗干扰强，验证直观，符合自动化工程师日常调试、点检和故障复位的实际工作节奏。</t>
+          <t>急停回路设计原则</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停按钮按下后设备未停止。具体情况：独立电源正常，但安全继电器底座端子氧化导致触点回路虚接，电压跌落至维持吸合阈值以下。解决思路：优先用万用表测安全输出端实测电压与电流，再逐段排查接线压接质量，而非先重刷PLC程序或更换模块。1个复杂问题概要：多台设备共用同一急停总线时，某台设备急停触发后其余设备延迟响应。具体问题：独立供电虽存在，但安全信号传输路径中混入了非安全等级的中间继电器，引入机械滞后和触点抖动。解决思路：核查所有串联在急停链路上的元器件是否具备安全等级认证，强制替换为经认证的安全触点或采用光耦隔离型安全信号转发模块，确保整条链路满足‘单点故障不导致安全功能丧失’的设计底线。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>安全回路设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>急停回路设计原则</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>请简单说说，安全门联锁逻辑中‘断电即制动’的设计意图是什么？</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>设计意图是确保一旦供电中断或控制信号丢失，设备立即停止运动并保持静止状态，防止因意外失能导致人员误入危险区域或机械继续动作造成伤害。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>目前主流有三种实现方式：一是通过安全继电器驱动失电抱闸型制动器，响应快、可靠性高，但需独立安全回路；二是用带安全功能的PLC模块直接控制伺服驱动器的安全扭矩关断STO，集成度高但依赖厂商生态；三是采用双通道硬接线串联急停与门锁触点，结构简单成本低，但诊断能力弱、扩展性差。综合来看，第一种方式在制造业产线中应用最广，兼顾响应时效、故障可诊断性和跨品牌兼容性，尤其适合多机型混线生产的自动化工程师日常维护场景。</t>
+          <t>安全门联锁逻辑</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门关闭后设备仍能启动。具体情况：门锁开关触点粘连或接线端子虚接，导致联锁信号始终为‘闭合’假象。解决思路：现场优先用万用表测量触点通断状态，并结合安全继电器输出指示灯交叉验证输入信号真实性。1个复杂问题概要：同一套联锁逻辑在不同班次频繁出现误停。具体问题：夜间照明线路干扰耦合进安全输入电缆，叠加接地不良引发共模噪声触发安全模块自保护。解决思路：排查现场接地连续性，加装屏蔽双绞线并单端接地，同时在安全输入前端增加抗扰型滤波模块，不依赖软件延时等软性补偿手段。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>一条柔性包装产线频繁出现运动轴定位偏差，排查发现上位机下发指令后，PLC与多个分布式驱动器之间的通信周期抖动超过允许阈值。请简述你从总线选型、物理层配置和协议栈参数三个层面，如何系统性优化通信确定性以满足微秒级运动控制精度要求。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>总线选型要优先选用支持硬实时同步机制的工业以太网类总线；物理层配置需确保双绞线阻抗匹配、终端电阻启用、拓扑结构为直线或星型且分支最短；协议栈参数应设置固定帧周期、关闭非必要服务、启用时间戳校准和抖动补偿功能。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>在总线选型上，EtherCAT因主站调度自主、从站处理零延迟而确定性最优；Profinet IRT虽依赖交换机支持但兼容性强，对现有设备改造友好；传统RS485类总线如Modbus RTU无法满足微秒级要求，应排除。物理层方面，屏蔽双绞线必须全程单点接地，避免环路干扰；连接器压接须规范，线缆长度超30米时需实测衰减并加装中继。协议栈参数中，将通信周期设为运动控制周期的整数分频，禁用诊断轮询和非周期数据通道，强制启用分布式时钟同步校准。综合来看，EtherCAT搭配规范布线与精简协议配置是当前产线升级中最可靠、实施成本可控的方案。</t>
+          <t>常见工业总线类型</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1个异常情况概要：通信周期突然跳变超阈值。具体情况：某驱动器节点偶尔失步，导致整个总线周期被拉长。解决思路：先隔离该节点做本地响应测试，确认是否为电源波动或散热不良引发从站时钟漂移，再检查其固件版本与主站兼容性。1个复杂问题概要：多轴协同时抖动呈规律性累积。具体问题：四轴同步插补中，第三轴通信延迟逐周期递增。解决思路：核查主站任务分配是否将运动控制任务与HMI刷新绑定在同一循环，拆分高优先级运动任务至独立周期，并验证驱动器内部滤波参数是否与总线更新节奏冲突。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>常见工业总线类型</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>在使用PROFINET构建主从站通信时，主站如何确保从站的输入数据在每个通信周期内被准确读取？请简述其核心机制。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>主站通过周期性轮询与确定性时间调度，在每个预设的通信周期开始时，统一触发所有已配置从站的输入数据采集，并严格按组态设定的顺序和时序完成整批数据的同步读取。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>实际工作中常用三种机制：一是基于IRT的硬件级时间同步，精度高、抖动小，适合高速运动控制场景，但对设备兼容性和网络拓扑要求严；二是RT协议下的软件调度，实施灵活、成本低，适用于中低速产线，但受CPU负载影响易出现微小延迟；三是DC同步机制，依赖时钟源校准各节点，稳定性好，但需主站与关键从站均支持且布线需避免强干扰。综合产线可靠性、调试效率与维护成本，当前主流产线优先采用RT协议配合合理周期配置，兼顾实时性与工程落地性。</t>
+          <t>主从站数据交换原理</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1个异常情况概要：从站输入数据偶发重复或跳变。具体情况：某伺服从站的编码器位置值在连续两个周期内未更新，或突变为零。解决思路：先确认该从站是否处于‘非活动’状态（如急停触发、驱动器故障锁存），再检查其端口LED状态及诊断缓冲区，重点排查供电波动、接线松动或终端电阻缺失。1个复杂问题概要：多轴协同场景下部分从站输入数据存在周期性偏移。具体问题：四轴搬运工作站中，第三轴的位置反馈总比其他轴晚半个周期。解决思路：核查主站组态中该从站的‘输入映像区起始地址’是否与其他轴错位，同步检查GSD文件版本一致性及IO控制器固件是否匹配，必要时重新执行‘网络扫描+参数下载’全流程。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>主从站数据交换原理</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>请简单说说Profinet设备在通信前，如何通过交换机识别彼此的物理端口位置。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Profinet设备在建立通信前，不依赖交换机主动识别彼此的物理端口位置；实际是由控制器（通常是PLC）通过参数化配置明确指定每个设备连接在哪个交换机端口上，交换机本身仅按MAC地址转发数据，不参与设备拓扑关系的自动发现或端口映射。</t>
+          <t>现场总线应用</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>在产线部署中，工程师常用三种方式确认端口对应关系：一是依据现场布线标签与机柜端子图人工核对，优点是可靠、无需额外工具，但耗时且易出错；二是使用支持LLDP协议的工业交换机配合调试软件读取端口连接信息，时效快、可视化强，但要求交换机和设备均启用该功能；三是通过PLC在线诊断界面查看各设备的‘端口路径’或‘拓扑状态’，直接关联到配置中的端口编号，最贴近实际运行逻辑，且与工程配置强一致。综合来看，第三种方式最符合自动化工程师日常维护和故障定位的实际需求，既保证时效性，又避免脱离控制系统语境。</t>
+          <t>Profinet通信机制</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1个异常情况概要：现场更换交换机后，PLC显示某设备‘端口不可达’但链路灯正常。具体情况：新交换机未启用LLDP或端口编号逻辑与原型号不同，导致PLC读取的端口标识与实际物理位置错位。解决思路：先在PLC中核对设备配置所绑定的端口号，再结合机柜接线图逐端口测试，必要时在交换机管理界面手动标注端口用途并同步更新工程文档。1个复杂问题概要：多级交换级联场景下无法准确定位故障设备所在物理端口。具体问题：二级交换机下挂多个从站，PLC只显示一级交换机端口号，无法穿透识别二级交换机上的具体接入位置。解决思路：分段启用交换机端口镜像功能，配合网络分析仪抓包比对源MAC与入端口关系；同时要求在初始布线阶段强制执行‘端口-设备-图纸’三者一一挂牌并录入资产台账，从源头保障可追溯性。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>现场总线应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Profinet通信机制</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>在调试一台PLC与变频器通过Modbus RTU通信时，发现变频器的运行频率读取值总是比实际显示低10倍，已确认通信参数和功能码正确，请简述最可能的原因及验证方法。</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>最可能的原因是PLC程序中对变频器频率寄存器的数值进行了错误的比例换算，把原始寄存器值直接当作Hz使用，而变频器实际以0.1Hz为最小单位存储该值，即寄存器值需乘以0.1才对应真实频率。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>常见处理方式有四种：一是检查变频器手册中频率寄存器的单位说明，确认是否为0.1Hz步进；二是用Modbus调试工具直接读取该寄存器原始值，对比面板显示值是否呈10倍关系；三是核对PLC程序中该寄存器对应的标定系数或缩放设置；四是临时修改PLC程序，将读取值乘以10后观察是否匹配。前两种侧重快速定位，后两种侧重闭环验证；其中结合调试工具直读寄存器加手册比对，时效性高、无需停机，是最推荐的首步动作。</t>
+          <t>寄存器地址映射</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1个异常情况概要：寄存器单位理解偏差。具体情况：不同品牌变频器对同一功能码（如运行频率）的寄存器单位定义不一致，有的用Hz整数，有的用0.1Hz整数，但PLC程序沿用旧项目配置未更新。解决思路：以当前变频器型号为准，查阅其最新版中文操作手册‘Modbus地址表’章节，锁定该寄存器的单位与量程说明，并同步更新PLC变量注释与标定逻辑。1个复杂问题概要：多品牌设备混用导致标定逻辑冲突。具体问题：产线升级后新增不同品牌变频器，PLC程序未按设备类型区分标定系数，统一套用旧系数造成批量读数偏差。解决思路：在PLC程序中建立设备类型标识位，根据通讯响应中的型号识别码或固定地址特征，动态调用对应标定参数表，确保同一通信通道内不同设备单位处理可配置、可追溯。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>寄存器地址映射</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>当Modbus TCP网关将RS-485侧多个从站映射到同一IP端口时，出现部分从站的功能码0x10写多个寄存器响应被主站丢弃。请简述你如何利用功能码0x10的字节数字段与后续数据长度的强一致性要求，结合TCP分包边界与RTU帧完整性校验机制，分析该现象的根本原因并提出验证路径。</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>功能码0x10的响应帧中，字节数字段必须严格等于后续实际写入字节数，且该字段值需与RTU帧尾部CRC校验覆盖范围完全匹配；TCP层不感知Modbus帧边界，若网关未按RTU帧完整单位拆分或拼接数据，会导致主站解析时字节数与后续数据长度不一致，触发协议层校验失败而丢弃响应。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>常见处理方式有四种：一是网关启用RTU帧级缓存与边界识别，确保每个响应帧独立封装后转发，时效性好但依赖固件支持；二是强制单从站独占TCP连接，避免混帧，实施简单但资源占用高、扩展性差；三是主站侧增加响应缓冲与重组装逻辑，开发成本高且不符合标准主站行为；四是通过抓包比对TCP负载与RTU帧结构，定位错位点。首选第一种，它在不改动主站的前提下，从网关侧根治帧完整性问题，符合产线现场快速复现、快速闭环的要求。</t>
+          <t>功能码识别</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1个异常情况概要：网关将两个RTU响应粘连发送。具体情况：RS-485侧两个从站响应被合并进同一TCP报文段，导致第二个响应的字节数字段指向错误偏移，主站解析失败。解决思路：用网络分析仪捕获TCP流，逐字节对照RTU帧结构，确认粘包位置，再核查网关映射配置中是否关闭了‘多从站响应聚合’选项。1个复杂问题概要：同一TCP连接下不同从站响应时序交错引发字节数字段错位。具体问题：网关未按从站ID顺序组织响应，造成后发出的短响应被截断嵌入前一帧末尾。解决思路：启用网关的‘响应队列隔离’模式，为每个从站分配独立应答缓冲区，并通过串口日志与TCP时间戳交叉比对验证时序一致性。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>功能码识别</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>某汽车焊装产线使用工业以太网连接机器人控制器与安全光栅，当光栅检测到人员闯入时，需在50毫秒内触发急停且确保控制器不误判瞬态干扰。请简述为满足该时效与可靠性要求，握手信号流程中信号边沿检测、确认延时设定和重试机制应如何协同设计。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>边沿检测应锁定光栅输出的上升沿作为有效触发起点；确认延时需设置在控制器侧，用于过滤短于阈值的抖动信号；重试机制不在单次急停流程中启用，仅用于通信链路异常恢复后的状态同步，且不得影响首次响应时效。</t>
+          <t>设备信号交互</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是纯硬件边沿捕获+固定滤波延时（5–10ms），响应快但抗干扰弱；二是控制器周期扫描+可配置去抖窗口（如20ms双稳态确认），兼顾时效与鲁棒性，是当前主流选择；三是带时间戳的事件驱动通信，依赖交换机支持微秒级时间同步，实施成本高且调试复杂。综合产线部署效率、维护习惯和故障复现能力，第二种最适用——它把确认逻辑放在控制器输入模块固件层，不增加编程负担，又能通过现场实测调整延时参数。</t>
+          <t>握手信号流程</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1个异常情况概要：光栅输出受焊接飞溅或电磁耦合引发亚毫秒级毛刺。具体情况：PLC输入端频繁出现宽度3–8ms的假边沿，导致偶发误停。解决思路：将边沿检测与确认延时绑定为原子操作，即仅当同一通道连续两次采样均维持高电平且间隔超设定阈值，才视为有效触发。1个复杂问题概要：急停信号发出后，因网络瞬断导致控制器未收到光栅释放确认。具体问题：复位时系统无法判断光栅是否真已恢复安全状态。解决思路：采用‘双通道状态比对’——光栅同时输出安全信号与自检心跳，控制器须同步满足‘安全信号回落+心跳持续更新’才允许复位，避免单点失效引发风险。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>设备信号交互</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>握手信号流程</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>在工业现场，当PLC与远程IO模块通过EtherCAT通信时，如果主站检测不到某个从站的心跳信号，通常会采取什么动作来判断该从站是否真的离线？请简述这个判断过程的核心依据。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>主站会连续多次尝试读取该从站的实时状态寄存器，并结合通信周期内该从站是否持续上报有效数据帧来综合判定；核心依据是：心跳信号的本质是周期性、可验证的双向应答行为，缺失即意味着从站未按约定节奏完成状态同步。</t>
+          <t>设备信号交互</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>常用判断方法有四种：一是延长单次扫描周期后重试，优点是操作简单，但无法区分瞬时干扰和真离线；二是切换至诊断模式主动发送链路探测指令，响应快且能排除总线拥堵干扰，但部分老旧模块不支持；三是检查本地供电与终端电阻状态，直接定位硬件异常，时效性强但需停机操作；四是比对相邻从站通信延迟突变情况，可间接反映物理链路中断点，无需干预设备，但依赖拓扑完整性。综合来看，优先采用‘诊断模式探测+本地供电目视确认’组合方式，在保障产线不停机前提下兼顾时效性与准确性。</t>
+          <t>心跳信号判断</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1个异常情况概要：从站供电正常但通信间歇性丢失。具体情况：现场测量端子电压稳定，但主站每3～5个周期偶发一次心跳超时。解决思路：重点排查该从站前端分支电缆的屏蔽层接地是否单点松动，或M12接头内部针脚是否存在微动氧化——这类问题在振动工况下极易引发虚接，需用红外热像仪辅助定位温升异常点。1个复杂问题概要：多个相邻从站同时心跳丢失。具体问题：并非单点故障，而是某段总线出现共模干扰或拓扑断裂。解决思路：立即调取主站EtherCAT拓扑扫描日志，定位通信断点位置，同步使用示波器在疑似断点两端抓取差分信号波形，确认是信号衰减还是共模噪声超标，再针对性更换带双层屏蔽的专用EtherCAT电缆或加装抗干扰磁环。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>设备信号交互</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>心跳信号判断</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>在基于OPC UA PubSub模式的分布式控制系统中，若某个发布节点因临时网络抖动失联，订阅端应依赖什么机制来保障数据连续性？请说明该机制如何支持通信中断后的状态恢复。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>订阅端应依赖内置的消息缓存与重传同步机制来保障数据连续性。该机制通过本地暂存已接收但尚未确认的最新有效数据，并在网络恢复后主动向发布端请求缺失时段的状态快照或增量更新，从而实现断连期间的数据补全和状态对齐。</t>
+          <t>通信异常诊断</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>实际工程中常用三种方式：一是仅靠心跳超时重连，恢复慢且易丢数据；二是启用发布端本地历史缓存并支持按时间戳回溯查询，时效性好但增加发布侧资源开销；三是订阅端自带滑动窗口缓存+断点续传协议，兼顾实时性和鲁棒性，是当前产线部署中最主流的选择。综合来看，第三种方式最适配自动化工程师日常维护场景——它不依赖发布端改造，调试直观，故障定位链路短，且与PLC周期扫描、伺服响应节拍天然兼容。</t>
+          <t>通信中断恢复</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1个异常情况概要：网络抖动导致部分心跳包丢失但TCP连接未断，订阅端误判为正常而停止触发重同步。具体情况：交换机QoS策略造成UDP心跳包优先级被降级，实际数据流仍在，但状态感知滞后。解决思路：将心跳监测与关键工艺变量变化率联合判断，设置双阈值触发缓存校验。1个复杂问题概要：多订阅端从同一发布源恢复时集中请求历史数据，引发发布节点瞬时过载。具体问题：三个包装工位的HMI同时重连，争抢同一台灌装PLC的历史数据块，导致其扫描周期延长超限。解决思路：在订阅端引入随机退避+分级请求策略，优先拉取最近5秒关键变量快照，再按需分批获取更早数据。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>通信异常诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>通信中断恢复</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>在产线PLC与伺服驱动器通过EtherCAT通信时，频繁出现周期性报文超时，已排除网络物理层故障，也确认主站任务周期稳定。请简述你将从哪三个关键维度系统排查超时原因，并说明每个维度下最可能的根因。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>我会聚焦三个关键维度：一是主站侧的实时任务调度与资源分配是否合理；二是从站设备——特别是伺服驱动器的配置与响应能力是否匹配当前通信负载；三是整个EtherCAT拓扑结构下的同步机制与帧处理时序是否协调一致。</t>
+          <t>通信异常诊断</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>第一维度看主站，重点查PLC任务优先级设置、中断响应延迟和循环扫描中是否嵌入了非确定性操作，比如未加锁的共享变量访问或动态内存分配，这类问题隐蔽但影响确定性；第二维度查伺服驱动器，关注其过程数据映射宽度、DC同步偏差设置及内部滤波参数，宽映射或过严的同步容差会直接拖慢响应；第三维度查拓扑，比如分支过多、节点数接近极限或终端电阻缺失导致信号反射累积，虽不显性断连，却使有效通信窗口持续收窄。综合来看，优先验证伺服侧配置最高效，因其改动成本低、见效快，且覆盖80%以上同类问题。</t>
+          <t>报文超时原因</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1个异常情况概要：伺服驱动器过程数据区配置过宽。具体情况：实际只需读取位置反馈和状态字，但配置了包含温度、电流谐波等冗余字节，导致每帧传输量超标，挤占下一个周期的处理时间。解决思路：精简PDO映射，仅保留产线控制必需的数据项，并验证同步模式下刷新率是否匹配。1个复杂问题概要：多轴协同场景下DC主时钟漂移叠加。具体问题：某台伺服因固件版本差异对分布式时钟校准响应滞后，造成局部时序滑动，在连续运行数小时后累积偏差触发周期性超时。解决思路：统一关键从站固件版本，启用主站侧DC诊断功能定位偏差源，必要时改用硬件时间戳触发方式替代纯软件同步。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>通信异常诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>报文超时原因</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>请简述报文中‘帧头’字段在通信故障诊断中的基本作用。</t>
+          <t>故障诊断与可靠性</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>在自动化现场排查通信异常时，帧头是报文最前端的固定标识字段，它的核心作用是帮助工程师快速确认接收到的数据是否为有效通信报文。只有帧头正确，后续数据才可能被设备正常解析；若帧头缺失、错位或内容异常，说明通信链路已在物理层或协议层出现中断、干扰或设备未响应。</t>
+          <t>通信故障诊断</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>现场常用三种识别方式：一是用便携式协议分析仪实时捕获并高亮显示帧头，响应快但依赖设备支持；二是通过PLC或HMI内置的通信诊断界面查看帧头校验状态，无需额外工具但信息粒度粗；三是调取控制器日志中带时间戳的原始报文片段，可回溯比对但需人工逐帧核对。综合来看，第一种方式时效性与准确性平衡最好，尤其适合产线停机抢修场景，能第一时间区分是线缆接触不良还是主站未发帧。</t>
+          <t>报文抓取分析</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1个异常情况概要：帧头周期性丢失。具体情况：同一总线上多个从站报文帧头间歇性消失，但物理连接无松动、电压正常。解决思路：优先排查主站输出驱动能力是否衰减，重点测量终端电阻阻值和分支电缆长度是否超出规范，而非直接更换线缆。1个复杂问题概要：帧头正确但后续数据全乱码。具体问题：示波器和分析仪均显示帧头字节完整，但负载数据无法解析，且错误持续数秒后自动恢复。解决思路：结合伺服驱动器运行状态判断是否因瞬时过载触发内部通信重同步机制，需同步采集轴电流、温度及主站发送间隔，验证是否由设备级保护动作引发协议重置。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>故障诊断与可靠性</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>通信故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>报文抓取分析</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>对一个EtherNet/IP显式消息通信失败的场景进行报文分析时，发现响应报文的通用报文头中服务代码为0x00，这表示什么含义？请结合实际调试过程说明它对故障定位的提示作用。</t>
+          <t>故障诊断与可靠性</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>服务代码为0x00，表示该响应报文不是对请求的正常应答，而是设备明确拒绝执行该服务请求，属于协议层的否定响应。</t>
+          <t>通信故障诊断</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>在产线调试中，我们通常会用三种方式交叉验证：一是直接查看PLC侧日志，确认是否发出合法请求；二是比对设备手册中该服务是否被支持、是否需前置使能；三是检查设备当前状态，比如是否处于未初始化、故障锁定或非运行模式。第一种方法最快但依赖日志完整性；第二种最可靠但需查阅最新版设备文档；第三种最直观但容易忽略隐性状态（如远程复位未完成）。综合来看，优先采用状态检查+手册核对组合，既保证时效性，又能覆盖多数现场异常。</t>
+          <t>报文抓取分析</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1个异常情况概要：设备未进入可通信状态。具体情况：伺服驱动器刚上电但未完成内部自检，或PLC尚未下发初始化命令，此时虽物理链路通，但设备主动返回0x00拒绝所有显式请求。解决思路：先确认设备运行指示灯和就绪信号，再检查PLC程序中是否执行了设备使能序列。1个复杂问题概要：多主站共用同一设备时服务冲突。具体问题：HMI和PLC同时向同一从站发配置类显式消息，后到请求被前序未完成事务阻塞，导致返回0x00。解决思路：在PLC程序中增加通信互斥机制，并在HMI侧设置请求退避策略，避免并发写入。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>故障诊断与可靠性</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>通信故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>报文抓取分析</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>在分析PROFINET IO设备周期性通信中断问题时，若抓取到多个RT数据帧中出现重复的帧序号，这通常反映哪类底层通信异常？请简述该现象与物理层或链路层问题的关联。</t>
+          <t>故障诊断与可靠性</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>这通常反映的是链路层的帧重传或缓冲区异常，本质是设备在发送或接收过程中未能按序可靠交付实时帧，导致上层协议栈误判并重复提交相同序号的帧。</t>
+          <t>通信故障诊断</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>常见排查方向有四个：一是检查交换机端口缓存溢出，会导致帧被丢弃后触发重发，但序号未更新；二是核查终端设备的实时任务调度异常，比如CPU过载或中断响应延迟，造成帧生成逻辑错乱；三是排查双工模式不匹配或自动协商失败，引发链路层误帧和重传；四是验证网线质量及连接可靠性，接触不良可能使部分帧校验失败后被链路层静默重发。其中，优先验证终端设备实时任务状态和交换机缓冲行为，因这两类问题在产线现场复现率最高、定位耗时最短，且能同步覆盖多数物理层诱因。</t>
+          <t>报文抓取分析</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1个异常情况概要：终端设备实时任务卡顿。具体情况：PLC或IO控制器在高负载下未能按时完成PN帧组装，导致同一周期帧被重复提交至发送队列。解决思路：调取设备运行日志确认CPU占用率与任务延迟时间，临时降低扫描周期或关闭非必要通信服务，验证帧序号是否恢复正常。1个复杂问题概要：环网冗余切换过程中的帧序号错乱。具体问题：媒体冗余协议切换瞬间，主备路径帧到达顺序紊乱，下游设备链路层未正确处理序列号跳变。解决思路：检查冗余管理器切换日志与时间戳，确认切换是否超出PROFINET RT允许的抖动范围，并调整冗余超时参数或升级固件以支持更稳定的序列号同步机制。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>故障诊断与可靠性</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>通信故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>报文抓取分析</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>当使用工业以太网抓包工具捕获到CANopen主站发给从站的SDO下载请求报文，但未收到应答，此时应重点检查报文中哪两个关键字段的取值是否符合规范？请简单说说理由。</t>
+          <t>故障诊断与可靠性</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>应重点检查‘对象字典索引’和‘子索引’这两个字段。因为SDO下载请求能否被从站正确识别并响应，完全取决于这两个字段是否指向从站实际支持且可写的对象地址；若任一字段超出从站对象字典范围、格式错误或指向只读/不存在条目，从站将直接丢弃该请求，不生成应答。</t>
+          <t>通信故障诊断</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>现场常用三种排查方式：一是用设备厂商提供的配置工具导出从站对象字典，逐项比对索引与子索引的有效性，覆盖全面但依赖工具权限；二是通过PLC编程环境在线读取从站EDS文件并校验地址映射，时效性强但需网络连通且配置一致；三是结合设备手册人工核对关键参数地址，最可靠但效率低、易遗漏。综合来看，第二种方式最适合产线快速复现与验证，兼顾准确性与调试节奏。</t>
+          <t>报文抓取分析</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>异常情况概要：索引值为0x1008（制造商硬件版本）却尝试写入。具体情况：该索引在绝大多数从站中为只读，主站误配为下载目标，导致从站静默丢包。解决思路：立即核查主站组态中的SDO目标地址属性，确认其‘可写性’标识是否与从站实际对象字典一致。复杂问题概要：同一索引不同子索引行为不一致。具体问题：例如0x2100子索引0可写，但子索引1返回ABORT而非超时，说明子索引1对应功能模块未使能或处于保护状态。解决思路：先确认从站当前工作模式及使能链路是否完整，再检查相关功能块的初始化状态与使能条件是否满足。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>故障诊断与可靠性</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>通信故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>报文抓取分析</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>当丝杠导轨机构用于垂直方向升降时，制动器失效瞬间负载自由下坠，导致丝杠反向冲击导轨滑块。请从机械自锁条件、制动响应时间与导轨动态承载能力三者耦合角度，说明为何仅靠增大丝杠导程角无法可靠避免此类损伤，并指出最关键的防护设计原则。</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>机械自锁只在静止或极低速下成立，而制动失效是突发动态工况；导程角增大虽提升理论自锁性，但会显著降低传动效率和响应带宽，反而加剧伺服系统对突变负载的调节滞后；同时，导轨滑块的动态承载能力不取决于丝杠是否自锁，而取决于冲击能量能否被结构及时耗散。</t>
+          <t>传动机构理解</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>常见应对方案有四种：一是加装独立机械抱闸，响应快但增加维护点；二是采用失电即抱死的电磁制动器并冗余供电，可靠性高但成本上升；三是引入重载缓冲油缸串联在升降链路中，能吸收冲击但占用空间大；四是通过伺服驱动器内置的下垂控制+电流限幅策略实时抑制反向转矩，实施快、无硬件改动，但依赖整机调试经验。综合时效性、鲁棒性和产线落地性，第四种配合第二种构成主辅双保险最优。</t>
+          <t>丝杠导轨机构</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1个异常情况概要：制动器触点氧化导致实际响应延迟超标；具体情况：现场环境湿度大或启停频次低时，电磁铁吸合面形成微氧化膜，使制动动作延后几十毫秒，恰好越过伺服电流环的抑制窗口；解决思路：在设备维保规程中强制加入季度级制动器通断测试，并将测试结果纳入设备健康档案。1个复杂问题概要：多轴协同升降中单轴制动失效引发连锁冲击；具体问题：某三轴堆垛机构中一轴坠落，通过横梁刚性传递冲击力，导致邻近导轨滑块瞬时过载变形；解决思路：在结构设计阶段就对升降主梁做模态解耦分析，设置轴间机械隔离段，并在控制逻辑中加入轴间状态互锁与急停信号硬线广播。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>传动机构理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>丝杠导轨机构</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>请简单说说斜楔夹紧方式依靠什么原理实现自锁。</t>
+          <t>机械结构与设备机构</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>斜楔夹紧方式依靠斜面摩擦角小于斜楔升角这一几何与摩擦条件来实现自锁，即当施加外力撤除后，斜楔不会因工件反作用力而自行松脱。</t>
+          <t>夹治具定位理解</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>在自动化产线的夹治具设计中，常见的自锁实现方案有三种：一是纯斜楔结构，靠斜面角度与材料摩擦系数匹配，结构简单、响应快，但对加工精度和表面状态敏感；二是斜楔+弹簧辅助预压，提升初始夹紧可靠性，但增加失效点且需定期校验弹力衰减；三是斜楔+机械挡块限位，可规避摩擦波动影响，但增加装配复杂度和空间占用。综合产线节拍、维护频次与长期稳定性要求，当前主流采用斜楔+精密导向槽配合微调垫片的方式，既保证自锁鲁棒性，又便于现场快速更换与标定。</t>
+          <t>夹紧方式判断</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹紧后出现缓慢回退。具体情况是设备连续运行数小时后，斜楔位置轻微偏移，导致夹紧力衰减。解决思路是检查导向槽磨损及斜楔接触面油膜残留，清洁并确认润滑类型是否符合干摩擦设计要求，必要时更换高耐磨涂层斜楔。1个复杂问题概要：同一套斜楔机构在不同工件批次间自锁稳定性波动。具体问题是工件定位基准面粗糙度或平面度存在批次差异，改变了实际接触摩擦状态。解决思路是将斜楔夹紧力监测信号接入产线SCADA系统，结合工件来料质检数据做趋势关联分析，动态调整气动/液压驱动压力阈值，而非依赖固定角度设计。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>机械结构与设备机构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>夹治具定位理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>夹紧方式判断</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>当一个矩形板类零件需要在机床上进行钻孔加工，且图纸明确要求孔位尺寸以左侧长边和底侧短边为基准，那么夹治具定位时应如何布置定位元件？请简单说说。</t>
+          <t>机械结构与设备机构</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>应采用‘一面两销’中的‘一面一长边一短边’三点定位方式：用底面作为主要定位面限制三个自由度，左侧长边设置一个垂直于该边的定位销或挡块限制一个自由度，底侧短边设置一个垂直于该边的定位销或挡块限制最后一个自由度，从而实现六点定位完整约束。</t>
+          <t>夹治具定位理解</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>实际工程中常用三种布置方案：一是底面+左侧长边挡块+底侧短边挡块，结构简单、调换方便，但挡块重复定位精度受磨损影响；二是底面+左侧长边圆柱销+底侧短边削边销，定位刚性好、重复性高，但销孔加工与装配要求严格；三是底面+左侧长边V型块导向+底侧短边弹性定位块，适合中小批量柔性切换，但需额外设计预压机构。综合来看，第二种方案最常用——它兼顾了定位精度、长期稳定性与自动化上下料适配性，尤其适配自动化工程师需协同产线节拍、保障连续运行的工作需求。</t>
+          <t>定位基准选择</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>异常情况概要：左侧长边或底侧短边存在毛刺或轻微变形，导致零件无法贴紧定位元件。具体情况：零件边缘微翘或飞边使基准边虚接触，引发钻孔位置系统性偏移。解决思路：在定位元件前端集成轻触式机械反馈结构，配合气动预压动作，在夹紧前完成自适应贴合确认。复杂问题概要：同一套夹治具需兼容多个相似矩形板零件，但各零件左侧长边与底侧短边的实际公差带叠加后，基准边理论位置浮动超0.05mm。具体问题：传统刚性定位无法覆盖公差变异，导致部分零件装夹后基准失准。解决思路：采用可调式基准边定位模块，通过伺服微调机构在线补偿基准边位置，由视觉初定位结果闭环驱动，确保不同零件均能复现图纸指定的基准关系。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>机械结构与设备机构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>夹治具定位理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>定位基准选择</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>请简单说说，气缸推拉机构中，换向阀的作用主要是什么？</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>换向阀的核心作用是控制压缩空气的流向，从而决定气缸活塞杆伸出还是缩回。</t>
+          <t>机械执行机构</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>在非标设备现场调试和维护中，常用三类换向阀方案：一是手动换向阀，适合调试初期单次动作验证，但无法接入自动控制；二是电磁换向阀，响应快、易集成PLC输出点，是当前主流选择，但需注意线圈电压匹配和防尘防水等级；三是带位置反馈的先导式换向阀，能回传阀芯状态，便于故障定位，但成本高、接线复杂。综合来看，电磁换向阀在可靠性、成本和系统集成度上最平衡，是自动化工程师在产线部署和快速迭代中最常选用的方案。</t>
+          <t>气缸推拉机构</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1个异常情况概要：气缸动作迟滞或不动作。具体情况：换向阀得电后气缸无响应，常见原因是阀芯卡滞、进气口过滤器堵塞或供气压力不足。解决思路：先确认PLC输出信号和阀端电压是否正常，再断气手动推动阀芯检查灵活性，同步检查前端空气处理单元的水杯积水和滤芯状态。1个复杂问题概要：多气缸协同动作时出现时序冲突。具体问题：例如夹紧与定位气缸因换向阀响应时间差异导致干涉或过定位。解决思路：优先通过PLC程序增加软起保停逻辑和最小动作间隔，若仍不稳定，则选用响应时间一致性更好的同批次电磁阀，并在气路中加装节流阀微调单侧速度，避免单纯依赖电气延时。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>机械执行机构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>气缸推拉机构</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>在非标设备中，当气缸推拉机构需要同时满足高速响应和高定位精度要求时，仅靠标准单作用气缸难以实现。请简述你如何通过机械结构与气路协同设计来解决这一矛盾，并说明关键设计依据。</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>标准单作用气缸依靠弹簧复位，响应速度受弹簧力与压缩空气动态充放气限制，无法兼顾快速动作与末端稳定停准；要同时实现高速响应和高定位精度，必须打破单气腔+弹簧的固有结构约束，转而采用可独立控制进排气、并辅以机械限位或阻尼调节的复合执行方案。</t>
+          <t>机械执行机构</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>常见做法有四种：一是改用双电控两位五通阀驱动双作用气缸，配合节流阀调速，优点是响应快、方向可控，但定位靠硬限位，重复精度受限；二是加装气动伺服定位气缸，内置磁环与位置反馈，靠闭环气压调节实现微动，精度高但成本高、调试复杂；三是机械上增设精密导向+缓冲挡块+弹性定位销组合，用结构刚性吸收惯性冲击，适合中速高重复场景；四是气路中集成比例调压阀与高速切换阀协同，前端保压维持位置，后端快速泄压启停。综合来看，第三种最常用——它不依赖高成本元器件，在非标设备现场调试周期短、故障率低、维护直观，且完全适配自动化工程师日常的机械装配、气路搭接与功能验证工作。</t>
+          <t>气缸推拉机构</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1个异常情况概要：气缸到位后出现小幅回弹。具体情况：缓冲结束瞬间，活塞杆因残余气压与机械间隙产生0.1～0.3毫米反向位移，影响装配压入或检测触发。解决思路：在气路末端加装带保压功能的单向节流阀，配合机械端面增加微预压弹性垫片，从气路锁止与结构补偿两方面同步抑制回弹。1个复杂问题概要：多工位节拍压缩下，同一气缸需在不同行程段执行差异化速度与停位要求。具体问题：例如前80%行程要快进，后20%要减速精停，且每次停位公差≤±0.05mm。解决思路：采用分段式气路设计——主气路设高速通径，另引一路经比例阀调控的辅助气路接入缸体无杆腔末端，通过PLC输出模拟量联动调节辅助气压，实现行程内气动力的动态分配，机械侧同步优化导轨刚性与缸体安装基准，确保力传递路径无变形。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>机械执行机构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>气缸推拉机构</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>在非标设备中，气缸推拉机构常用于实现工件的定位夹紧。当需要确保气缸活塞杆伸出后能稳定保持位置、不受外力影响时，通常会采用哪种基础控制方式？请简述其工作原理。</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>通常采用双电控两位五通电磁阀配合机械自锁气缸，或单电控阀配气控单向阀（即气动锁紧回路）的基础控制方式。其核心原理是：通过切断进排气通路，将压缩空气封闭在气缸有杆腔或无杆腔内，利用气体不可压缩性形成刚性支撑，使活塞杆在断电、断信号状态下仍能抵抗外力位移。</t>
+          <t>机械执行机构</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>实际工程中有四种常用方案：一是双电控阀+普通气缸，靠两个线圈交替得电维持位置，断电易失位，适合短时保压；二是单电控阀+气控单向阀回路，结构简单成本低，但保压精度受密封性影响；三是带内置制动器的锁紧气缸，响应快、刚性强，但价格高、维修难；四是PLC控制比例阀配合压力闭环，动态补偿泄漏，适合高精度长时保压。综合来看，在非标设备中，气控单向阀构成的气动锁紧回路最常用——它不依赖外部电源与控制器，故障率低，调试快，完全满足90%以上夹紧定位场景对可靠性与交付周期的要求。</t>
+          <t>气缸推拉机构</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1个异常情况概要：保压期间活塞杆缓慢缩回。具体情况：气缸内泄漏或气控单向阀密封失效，导致腔内气压衰减。解决思路：先做空载保压测试判断泄漏点，再分段排查阀体密封、气管接头、缸筒磨损，优先更换O型圈和阀芯组件。1个复杂问题概要：夹紧过程中突发振动导致定位偏移。具体问题：工件刚性不足或夹紧力分布不均，引发共振叠加气路响应滞后。解决思路：在气路中加装微型缓冲节流阀调节进出气速度，同步优化夹具支撑点布局，必要时增加机械限位辅助稳态，避免单纯提高气压加剧冲击。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>机械执行机构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>气缸推拉机构</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>请简单说明，为什么接近开关用于检测金属工件到位时，其感应面应正对工件运动方向的前端面？</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>因为接近开关的感应区域集中在感应面正前方有限距离内，且有效检测依赖于金属工件进入该区域；若斜装或侧装，工件可能在未完全到位时就触发、或到位后仍未触发，导致定位误判。</t>
+          <t>机电接口设计</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>实际安装中常见四种方式：一是正对前端面垂直安装，响应及时、重复性好，但需预留足够安装空间；二是斜向45度安装，节省空间但易受工件姿态微变影响，检测稳定性下降；三是安装在工件侧面，仅适用于宽厚工件且需加厚感应头，抗干扰能力弱；四是双开关冗余布置，提升可靠性但增加布线与调试成本。综合时效性、稳定性与现场适配性，正对前端面垂直安装仍是非标设备中最常用、最稳妥的选择。</t>
+          <t>传感器安装位置</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1个异常情况概要：工件到位但接近开关不动作。具体情况：工件前端有油污、涂层或非金属附着物，削弱了金属对磁场的扰动效应。解决思路：优先清洁工件检测面，同步验证开关感应距离是否因安装松动或温度漂移而衰减，必要时更换为带抗污染涂层的感应头。1个复杂问题概要：多品种工件共用同一工位时检测一致性差。具体问题：不同厚度、材质或前端形状的工件导致触发位置波动超过±0.3mm，影响后续装配精度。解决思路：采用可调触发阈值的模拟量接近开关配合PLC软件补偿，或改用带IO-Link接口的智能开关，在换型时自动调用预设检测参数。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>机电接口设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>传感器安装位置</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>请简单说说，相机标定过程中‘内参’主要包含哪三个基本参数？</t>
+          <t>设备软件</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>内参主要包含三个基本参数：焦距、主点坐标、像素尺寸比例。其中焦距反映镜头成像的缩放关系；主点坐标是图像坐标系原点在像素平面上的实际位置；像素尺寸比例用于校正图像传感器上横向与纵向像素物理尺寸不一致带来的形变。</t>
+          <t>机器视觉集成</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>在产线视觉检测场景中，常用三种标定方式：棋盘格单次静态标定、带机械臂联动的多视角动态标定、以及基于产线固定工装的在线周期性复标。棋盘格标定实施快、精度稳，但依赖人工摆放，产线停机时间长；多视角动态标定可减少停机，但需同步运动控制信号，对PLC与视觉系统时序一致性要求高；工装在线复标无需停机，靠固定基准块自动触发，稳定性好，但前期需验证工装重复定位精度。综合来看，工装在线复标最适合自动化工程师日常维护——它把标定从‘项目阶段任务’转化为‘产线运行保障动作’，响应快、容错强、可纳入设备预防性维护计划。</t>
+          <t>相机标定方法</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>异常情况概要：标定后图像出现明显桶形畸变。具体情况：同一型号相机在不同产线部署后，检测结果波动大，复查发现边缘区域测量值系统性偏大。解决思路：不是重做标定，而是检查镜头安装是否松动或存在微小轴向偏移，优先紧固镜头接口并复测工装基准点，避免盲目调整软件参数。复杂问题概要：多相机协同测量时内参不统一导致拼接误差超差。具体问题：两条装配线共用一套视觉引导系统，但A线相机刚完成镜头更换，B线未同步更新内参，导致抓取位姿偏差。解决思路：建立内参版本台账，绑定相机ID与设备台账，在每次硬件变更后强制触发内参校验流程，并与MES报工动作联动，确保参数更新与物理变更同步生效。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>设备软件</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>机器视觉集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>相机标定方法</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>请简单说说视觉系统通过以太网与PLC交互时，通常采用哪种标准协议？</t>
+          <t>机器视觉应用</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>在制造业自动化产线中，视觉系统与PLC通过以太网交互时，最常用的是基于TCP/IP的自定义报文协议——也就是双方按约定的数据结构、地址映射和通信时序，直接收发二进制或结构化数据包。</t>
+          <t>视觉系统集成</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>实际工程中主要有四种做法：一是用PLC厂商原生支持的开放式以太网协议，比如西门子S7通信或三菱MC协议，优势是集成度高、调试快，但跨品牌兼容性差；二是走通用工业协议如EtherNet/IP或PROFINET，适合已有对应总线架构的产线，但视觉设备需内置对应协议栈，选型受限且成本高；三是采用轻量级MQTT或HTTP API方式，适合上位机中转场景，灵活性好但实时性难保障；四是主流做法——用标准TCP/UDP自定义报文，由视觉软件提供可配置的寄存器映射界面，PLC侧用原生Socket指令收发，兼顾实时性、通用性与实施效率，是当前产线集成中最稳妥、复用率最高的方案。</t>
+          <t>视觉与PLC交互方式</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1个异常情况概要：视觉系统发送数据后PLC收不到响应。具体情况是网络能通、端口开放，但PLC侧始终未触发接收完成标志。解决思路是先确认双方字节序是否一致，再检查PLC接收缓冲区是否溢出导致丢包，最后验证视觉端是否启用了发送确认机制并等待超时。1个复杂问题概要：多工位共用同一视觉系统时，PLC请求与视觉结果错位。具体问题是A工位触发拍照后，B工位的PLC却收到了该图像的检测结果。解决思路是必须在通信报文中嵌入唯一工位ID及时间戳，PLC侧严格校验ID匹配后再取用结果，并在视觉端启用请求-应答队列绑定机制，杜绝结果串扰。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>机器视觉应用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>视觉系统集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>视觉与PLC交互方式</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>某金属结构件焊接产线拟升级为自动焊，但现场发现不同批次工件的装配间隙偏差达±0.8mm，夹具重复定位精度为±0.3mm，而所选焊枪最小起弧间隙要求为±0.2mm。请简述你将如何综合工艺公差链、设备能力与质量验收标准，判断该自动化方案是否具备工程落地前提。</t>
+          <t>方案可行性与立项</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>作为自动化工程师，我会先厘清三类公差的叠加关系：工件装配间隙是输入变量，夹具定位精度决定工件在工装上的实际位置稳定性，焊枪起弧间隙是工艺执行的刚性门槛。三者共同构成影响自动焊接能否稳定引弧和成形的工艺公差链，必须整体评估是否满足质量验收对首焊点成功率和过程一致性的基本要求。</t>
+          <t>需求分析与可行性评估</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>常见应对路径有四种：一是优化夹具加装自适应浮动机构，在不更换主体结构前提下提升工件就位容差；二是引入视觉引导系统实时补偿工件位置偏移，但需评估节拍影响和现场光照干扰；三是调整焊枪选型或工艺参数，选用起弧容差更宽的焊枪或脉冲燃弧模式；四是推动前端装配工序收紧公差，但涉及跨部门协同周期长。综合来看，优先采用‘夹具柔性化+视觉辅助’组合方案，既保障当前产线节拍，又避免推翻既有工艺体系，落地时效性和兼容性最优。</t>
+          <t>产线工艺需求分析</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹具定位精度实测波动超出标称值。具体情况：夹具长期使用后机械磨损导致重复定位离散度增大，实测达±0.45mm。解决思路：快速开展夹具关键接触面状态检查与简易修配，同步建立夹具精度月度点检机制，不依赖返厂维修。1个复杂问题概要：多源公差耦合导致首焊点失败率超限。具体问题：工件间隙、夹具偏移、焊枪姿态误差在空间上非线性叠加，单一环节改进无法稳定起弧。解决思路：在试运行阶段设置三层验证——空载工况下测焊枪轨迹与理论间隙吻合度，加载典型工件做10组起弧测试，再结合首件焊缝金相与熔深数据反推公差分配合理性，闭环修正公差链模型。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>方案可行性与立项</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>需求分析与可行性评估</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>产线工艺需求分析</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>一台新购入的自动检测设备标称节拍为15秒/件，但实际运行中平均达到18秒/件。在评估其投资可行性时，这个差异会对回报测算产生什么实质性影响？请简述原因。</t>
+          <t>方案可行性与立项</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>节拍每延长3秒，意味着单位时间产量下降20%，直接影响年产出量和对应收入；同时，设备未达预期效率，会拉长投资回收周期，削弱项目经济性结论的可信度。</t>
+          <t>需求分析与可行性评估</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>常见评估方式有三种：一是基于实测节拍重新推算全年有效产出，最直接但需排除调试期干扰；二是对比同类产线历史运行数据做偏差归因，能识别是设备本身还是配套环节拖累；三是按最小可行节拍做敏感性分析，设定16秒、17秒、18秒三档测算回报区间。其中第一种最稳妥，前提是已稳定运行至少72小时且无非计划停机，兼顾时效与依据充分性。</t>
+          <t>自动化导入投资回报判断</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>异常情况概要：设备刚上线即出现节拍劣化，但供应商坚称属正常磨合。具体情况：实测18秒含频繁复位和图像重采样，非标定工况。解决思路：立即冻结验收流程，联合工艺与质量部门确认检测项是否被隐性增加，而非单纯归因于设备。复杂问题概要：节拍不稳，波动范围达15–25秒。具体问题：同一产品批次内节拍离散大，说明触发逻辑或信号同步存在系统性偏差。解决思路：不急于调参数，先回溯PLC主控时序日志与传感器响应时标，定位是上游来料定位偏差还是本机判定阈值漂移，再针对性优化控制策略。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>方案可行性与立项</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>需求分析与可行性评估</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>自动化导入投资回报判断</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>某包装线伺服电机在联调时出现间歇性失步，示波器观测到驱动器使能信号存在毫秒级抖动，但PLC程序逻辑与硬件接线均复核无误。请结合信号链路完整性要求，说明你将如何定位该抖动的真实源头，并解释为何不能仅依赖PLC侧诊断。</t>
+          <t>现场联调</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>信号链路完整性要求使能信号从PLC输出端出发，经端子排、中间继电器（如有）、线缆、插头连接器，最终稳定到达伺服驱动器输入端，全程不得引入干扰、压降、接触不良或时序畸变。</t>
+          <t>设备故障诊断</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>我会分三段排查：第一段查PLC输出模块后端——用示波器探头直接夹在PLC输出端子上测原始波形，确认是否源头已抖动；第二段查中间环节——重点检测端子压接是否松动、线缆是否与动力线平行走线过长、插头是否存在氧化或针脚缩针；第三段查驱动器侧接口——测量驱动器使能端口的供电参考地是否浮动、共模抑制能力是否被削弱。不单靠PLC诊断，是因为PLC只能反馈自身输出指令状态，无法感知物理层信号畸变，比如接触电阻变化引起的电压跌落、高频耦合导致的边沿抖动，这些在PLC内部逻辑里完全不可见。</t>
+          <t>信号链路排查</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1个异常情况概要：端子排螺丝虚紧。具体情况：多股线未搪锡、拧紧力矩不足，通电发热后微形变导致接触电阻周期性跳变，引发毫秒级电压跌落。解决思路：逐点红外测温初筛，再用毫伏档测带载压降，替换为弹簧压接端子并做扭矩标定。1个复杂问题概要：同一控制柜内多台伺服共用使能信号分支走线。具体问题：分支点存在阻抗不连续，高频反射叠加在使能沿上，仅在特定负载组合下激发抖动。解决思路：改用点对点独立布线，驱动器侧加RC缓冲电路，并用示波器眼图法验证信号完整性。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>现场联调</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>设备故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>信号链路排查</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>一条装配线的气动夹具在联调中响应延迟明显，IO模块输入信号上升沿与电磁阀动作之间存在120ms偏差，已确认PLC扫描周期为10ms。请说明你将如何分段隔离信号链路中的延时环节，并指出哪些环节必须实测而非依赖手册参数。</t>
+          <t>现场联调</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>我会把整个信号链路按物理顺序拆成四段：从传感器触发开始，到PLC输入端子接收信号；PLC内部处理（含程序扫描和输出刷新）；PLC输出端子到IO模块驱动电路；IO模块输出到电磁阀线圈得电动作。每一段的起止点都对应实际可接触的硬件接口或测试点。</t>
+          <t>设备故障诊断</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>常用排查方法有三种：一是用示波器同步捕获输入端子和电磁阀两端电压波形，直接定位延时所在段，时效高但需现场带设备；二是逐段短接信号、旁路逻辑，观察延迟是否消失，操作简单但可能掩盖真实时序问题；三是用PLC自带诊断功能读取各IO点状态变化时间戳，依赖系统支持且精度有限。综合来看，第一种方法最可靠，能在一次测量中覆盖全部环节，且符合现场联调快速闭环的要求。</t>
+          <t>信号链路排查</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1个异常情况概要：IO模块驱动电路存在隐性滤波设计。具体情况是厂家手册未标注输入滤波时间，但实测发现光耦前端加了RC延时电路，导致信号滞后约40ms。解决思路是拆开模块外壳，在输入引脚处直接测量光耦初级侧波形，确认是否由硬件滤波引起。1个复杂问题概要：电磁阀本体响应非线性。具体问题是阀芯启闭受气压、负载摩擦和老化影响，相同电信号下动作时间波动大。解决思路是在标准气压和空载工况下，用高速摄像头配合光电开关实测阀杆位移起始时刻，把机械响应时间从电气链路中剥离出来单独标定。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>现场联调</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>设备故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>信号链路排查</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>一条锂电池模组装配线在终验收阶段，安全光栅响应时间实测为32ms，略超国标GB/T 15706规定的30ms限值，但整机已通过CE认证且无历史安全事故。请简述你依据哪些维度交叉验证，才能确认该指标是否构成不可妥协的验收判定红线？</t>
+          <t>现场联调</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>作为自动化工程师，在设备终验收阶段，需从安全功能完整性、风险场景匹配性、系统集成约束性三个基本维度交叉验证：一是该光栅所保护的具体危险动作（如压合、入壳、热压等）对应的人体可及路径与反应时间是否实际允许32ms；二是整条线的急停链路、控制器扫描周期、信号传输路径是否形成叠加延迟；三是现场实际工况下操作人员行为模式（如频繁介入频次、防护门开关逻辑）是否放大该延迟风险。</t>
+          <t>设备验收理解</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>常用验证方法有四种：第一是现场模拟触发测试，复现典型误入动作并同步采集PLC输入中断至执行器切断的端到端时序，时效高但仅反映单点工况；第二是基于产线节拍与人机交互频率的风险再评估，覆盖动态使用场景但依赖经验判断；第三是调取安全控制器日志与硬件手册，核查响应时间是否含诊断延迟或滤波冗余，数据准但需供应商配合；第四是组织跨职能联合评审，整合工艺、EHS、生产代表意见，全面但耗时。综合来看，应以现场模拟测试为基准，辅以人机交互频率分析，兼顾效率与覆盖性。</t>
+          <t>验收判定标准</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1个异常情况概要：光栅响应时间合格但现场仍出现防护失效。具体情况：测试时未考虑光电干扰或电缆敷设导致的信号抖动，使实际响应波动超出30ms阈值。解决思路：在产线空载与满载两种状态下重复三次以上触发测试，并检查信号线是否与动力线隔离敷设。1个复杂问题概要：多安全器件串联导致累积延迟超标。具体问题：光栅+安全继电器+伺服抱闸回路串联后，总切断时间达45ms，远超单一器件限值。解决思路：重构安全链路，将光栅直连安全PLC的专用输入通道，驱动伺服使能切断与机械制动分路径控制，避免级联延迟叠加。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>现场联调</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>设备验收理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>验收判定标准</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>某产线关键装配设备近三个月的故障记录显示：第一次停机42小时后修复，第二次停机18小时后修复，第三次停机66小时后修复。请结合这三次故障间隔的实际运行时间，说明如何正确计算该设备的平均无故障时间，并指出若将停机修复时间误计入运行时间会导致什么偏差。</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>平均无故障时间，也就是常说的MTBF，指的是设备两次相邻故障之间实际正常运转的时间平均值。它只统计设备从修复完成重新投入运行，到下一次发生故障之间的那段有效工作时长，不包含任何停机、维修、等待或调试时间。</t>
+          <t>设备可靠性分析</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>在产线现场，常用三种方式获取运行时间：一是通过设备PLC内置运行计时器读取真实带载运行秒数；二是利用SCADA系统采集主轴/气缸动作周期叠加推算有效作业时长；三是结合MES工单执行记录反推设备空转与负载时段。第一种最准确但依赖PLC程序规范性；第二种覆盖全面但需校准传感器响应延迟；第三种易获取但可能混入换型等待时间。综合来看，优先采用PLC运行计时器数据，再用MES工单做交叉验证，既保障时效性又兼顾可追溯性。</t>
+          <t>MTBF指标含义</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1个异常情况概要：运行时间数据源存在断点或人为清零。具体情况：PLC计时器因断电重启被重置，或运维人员误操作清零，导致连续运行时段被割裂成多个短周期，MTBF被严重低估。解决思路：启用带电池保持的累计运行寄存器，并设置断点自动续记逻辑，同时在SCADA端增加运行时长趋势突变告警。1个复杂问题概要：设备处于多班次交替运行且存在计划性停机。具体情况：白班运行8小时后停机交接，夜班再启动，但交接间隙未触发故障，却造成‘运行中断’假象。解决思路：将班次交接、换模、清洁等计划内停机统一标记为非故障态，并在计算时仅截取连续有效运行段落，按实际故障起止点切分运行区间。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>设备可靠性分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MTBF指标含义</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
